--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I988"/>
+  <dimension ref="A1:I989"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31067,6 +31067,37 @@
         <v>3</v>
       </c>
       <c r="I988" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C989" t="n">
+        <v>14</v>
+      </c>
+      <c r="D989" t="n">
+        <v>27</v>
+      </c>
+      <c r="E989" t="n">
+        <v>34</v>
+      </c>
+      <c r="F989" t="n">
+        <v>36</v>
+      </c>
+      <c r="G989" t="n">
+        <v>47</v>
+      </c>
+      <c r="H989" t="n">
+        <v>3</v>
+      </c>
+      <c r="I989" t="n">
         <v>4</v>
       </c>
     </row>
@@ -31109,7 +31140,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.65</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="3">
@@ -31117,10 +31148,10 @@
         <v>34</v>
       </c>
       <c r="B3" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C3" t="n">
-        <v>11.45</v>
+        <v>11.54</v>
       </c>
     </row>
     <row r="4">
@@ -31131,7 +31162,7 @@
         <v>113</v>
       </c>
       <c r="C4" t="n">
-        <v>11.45</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="5">
@@ -31142,7 +31173,7 @@
         <v>112</v>
       </c>
       <c r="C5" t="n">
-        <v>11.35</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="6">
@@ -31153,7 +31184,7 @@
         <v>110</v>
       </c>
       <c r="C6" t="n">
-        <v>11.14</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="7">
@@ -31164,7 +31195,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.14</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="8">
@@ -31175,7 +31206,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>11.04</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="9">
@@ -31186,7 +31217,7 @@
         <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>10.84</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="10">
@@ -31197,7 +31228,7 @@
         <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>10.84</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="11">
@@ -31208,7 +31239,7 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.74</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="12">
@@ -31219,7 +31250,7 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>10.74</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="13">
@@ -31230,7 +31261,7 @@
         <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>10.64</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="14">
@@ -31241,7 +31272,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.64</v>
+        <v>10.63</v>
       </c>
     </row>
     <row r="15">
@@ -31252,7 +31283,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.54</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="16">
@@ -31263,29 +31294,29 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.54</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B17" t="n">
         <v>103</v>
       </c>
       <c r="C17" t="n">
-        <v>10.44</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C18" t="n">
-        <v>10.33</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="19">
@@ -31296,7 +31327,7 @@
         <v>101</v>
       </c>
       <c r="C19" t="n">
-        <v>10.23</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="20">
@@ -31307,7 +31338,7 @@
         <v>101</v>
       </c>
       <c r="C20" t="n">
-        <v>10.23</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="21">
@@ -31318,7 +31349,7 @@
         <v>101</v>
       </c>
       <c r="C21" t="n">
-        <v>10.23</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="22">
@@ -31329,7 +31360,7 @@
         <v>101</v>
       </c>
       <c r="C22" t="n">
-        <v>10.23</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="23">
@@ -31340,7 +31371,7 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.23</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="24">
@@ -31351,7 +31382,7 @@
         <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>10.13</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="25">
@@ -31362,7 +31393,7 @@
         <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="26">
@@ -31373,7 +31404,7 @@
         <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="27">
@@ -31384,7 +31415,7 @@
         <v>99</v>
       </c>
       <c r="C27" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="28">
@@ -31395,7 +31426,7 @@
         <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>9.93</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="29">
@@ -31406,7 +31437,7 @@
         <v>98</v>
       </c>
       <c r="C29" t="n">
-        <v>9.93</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="30">
@@ -31417,7 +31448,7 @@
         <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="31">
@@ -31428,7 +31459,7 @@
         <v>97</v>
       </c>
       <c r="C31" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="32">
@@ -31439,29 +31470,29 @@
         <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="B33" t="n">
         <v>96</v>
       </c>
       <c r="C33" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="B34" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.630000000000001</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -31472,7 +31503,7 @@
         <v>94</v>
       </c>
       <c r="C35" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="36">
@@ -31483,7 +31514,7 @@
         <v>94</v>
       </c>
       <c r="C36" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="37">
@@ -31494,7 +31525,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.42</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="38">
@@ -31505,7 +31536,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.42</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="39">
@@ -31516,7 +31547,7 @@
         <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.42</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="40">
@@ -31527,7 +31558,7 @@
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.42</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="41">
@@ -31538,7 +31569,7 @@
         <v>92</v>
       </c>
       <c r="C41" t="n">
-        <v>9.32</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="42">
@@ -31549,7 +31580,7 @@
         <v>91</v>
       </c>
       <c r="C42" t="n">
-        <v>9.220000000000001</v>
+        <v>9.210000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -31560,7 +31591,7 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -31571,7 +31602,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.119999999999999</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -31582,29 +31613,29 @@
         <v>89</v>
       </c>
       <c r="C45" t="n">
-        <v>9.02</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B46" t="n">
         <v>88</v>
       </c>
       <c r="C46" t="n">
-        <v>8.92</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C47" t="n">
-        <v>8.81</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="48">
@@ -31620,7 +31651,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B49" t="n">
         <v>87</v>
@@ -31634,10 +31665,10 @@
         <v>36</v>
       </c>
       <c r="B50" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C50" t="n">
-        <v>8.609999999999999</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -31690,7 +31721,7 @@
         <v>212</v>
       </c>
       <c r="C2" t="n">
-        <v>21.48</v>
+        <v>21.46</v>
       </c>
     </row>
     <row r="3">
@@ -31698,10 +31729,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.47</v>
+        <v>20.55</v>
       </c>
     </row>
     <row r="4">
@@ -31712,7 +31743,7 @@
         <v>195</v>
       </c>
       <c r="C4" t="n">
-        <v>19.76</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="5">
@@ -31723,7 +31754,7 @@
         <v>192</v>
       </c>
       <c r="C5" t="n">
-        <v>19.45</v>
+        <v>19.43</v>
       </c>
     </row>
     <row r="6">
@@ -31731,10 +31762,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C6" t="n">
-        <v>18.84</v>
+        <v>18.93</v>
       </c>
     </row>
     <row r="7">
@@ -31745,7 +31776,7 @@
         <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>18.54</v>
+        <v>18.52</v>
       </c>
     </row>
     <row r="8">
@@ -31756,7 +31787,7 @@
         <v>179</v>
       </c>
       <c r="C8" t="n">
-        <v>18.14</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="9">
@@ -31767,7 +31798,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.92</v>
+        <v>16.9</v>
       </c>
     </row>
     <row r="10">
@@ -31778,7 +31809,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.51</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="11">
@@ -31789,7 +31820,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>14.89</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="12">
@@ -31800,7 +31831,7 @@
         <v>83</v>
       </c>
       <c r="C12" t="n">
-        <v>8.41</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="13">
@@ -31811,7 +31842,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
   </sheetData>
@@ -31853,7 +31884,7 @@
         <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>20.43</v>
+        <v>20.39</v>
       </c>
     </row>
     <row r="3">
@@ -31861,10 +31892,10 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.57</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="4">
@@ -31875,7 +31906,7 @@
         <v>83</v>
       </c>
       <c r="C4" t="n">
-        <v>17.85</v>
+        <v>17.81</v>
       </c>
     </row>
     <row r="5">
@@ -31886,7 +31917,7 @@
         <v>80</v>
       </c>
       <c r="C5" t="n">
-        <v>17.2</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="6">
@@ -31897,7 +31928,7 @@
         <v>78</v>
       </c>
       <c r="C6" t="n">
-        <v>16.77</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="7">
@@ -31908,7 +31939,7 @@
         <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>16.77</v>
+        <v>16.74</v>
       </c>
     </row>
     <row r="8">
@@ -31919,7 +31950,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.34</v>
+        <v>16.31</v>
       </c>
     </row>
     <row r="9">
@@ -31930,7 +31961,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>15.91</v>
+        <v>15.88</v>
       </c>
     </row>
     <row r="10">
@@ -31938,10 +31969,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C10" t="n">
-        <v>15.27</v>
+        <v>15.45</v>
       </c>
     </row>
     <row r="11">
@@ -31952,7 +31983,7 @@
         <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>15.05</v>
+        <v>15.02</v>
       </c>
     </row>
     <row r="12">
@@ -31963,7 +31994,7 @@
         <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>14.84</v>
+        <v>14.81</v>
       </c>
     </row>
     <row r="13">
@@ -31974,7 +32005,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.98</v>
+        <v>13.95</v>
       </c>
     </row>
   </sheetData>
@@ -32056,7 +32087,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6 &amp; 49</t>
+          <t>14 &amp; 34</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -32066,7 +32097,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1 &amp; 7</t>
+          <t>6 &amp; 49</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -32076,7 +32107,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11 &amp; 23</t>
+          <t>1 &amp; 7</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -32086,7 +32117,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21 &amp; 34</t>
+          <t>11 &amp; 23</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -32096,17 +32127,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>16 &amp; 34</t>
+          <t>21 &amp; 34</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20 &amp; 21</t>
+          <t>16 &amp; 34</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -32116,7 +32147,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14 &amp; 34</t>
+          <t>20 &amp; 21</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -32470,13 +32501,13 @@
         <v>32</v>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
         <v>10.3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="3">
@@ -32484,13 +32515,13 @@
         <v>38</v>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
         <v>9.9</v>
       </c>
       <c r="D3" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="4">
@@ -32498,13 +32529,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
         <v>10.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="5">
@@ -32512,13 +32543,13 @@
         <v>18</v>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>2.67</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="6">
@@ -32526,181 +32557,181 @@
         <v>29</v>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>10.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
-        <v>11.2</v>
+        <v>9.9</v>
       </c>
       <c r="D7" t="n">
-        <v>1.88</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>10.4</v>
+        <v>8.9</v>
       </c>
       <c r="D9" t="n">
-        <v>1.82</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>11.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.57</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>10.3</v>
+        <v>8.4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>9.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="D13" t="n">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B15" t="n">
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>10.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>0.93</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>8.4</v>
+        <v>10.3</v>
       </c>
       <c r="D16" t="n">
-        <v>1.19</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.08</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B18" t="n">
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>8.699999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="D18" t="n">
-        <v>1.04</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="19">
@@ -32708,150 +32739,150 @@
         <v>1</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
         <v>9.1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.88</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B20" t="n">
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B21" t="n">
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B22" t="n">
         <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="D22" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="B23" t="n">
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="D23" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n">
         <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>10.2</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="B25" t="n">
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="D25" t="n">
-        <v>0.78</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>9.4</v>
+        <v>11.3</v>
       </c>
       <c r="D26" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B27" t="n">
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.58</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="B28" t="n">
         <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>11.3</v>
+        <v>10.6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B29" t="n">
         <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="D29" t="n">
         <v>0.55</v>
@@ -32862,125 +32893,125 @@
         <v>22</v>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
         <v>10.1</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>10.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.46</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="D32" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>11.2</v>
+        <v>12.3</v>
       </c>
       <c r="D34" t="n">
-        <v>0.36</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="D35" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="39">
@@ -32988,122 +33019,122 @@
         <v>49</v>
       </c>
       <c r="B39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C39" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>0.21</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="B42" t="n">
         <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>8.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>9.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="D43" t="n">
-        <v>0.22</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="D44" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>8.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D45" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>11.2</v>
+        <v>9.5</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33111,13 +33142,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>9.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33125,13 +33156,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>10.4</v>
+        <v>11.3</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33139,13 +33170,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33153,13 +33184,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I989"/>
+  <dimension ref="A1:I990"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31099,6 +31099,37 @@
       </c>
       <c r="I989" t="n">
         <v>4</v>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="1" t="n">
+        <v>46276</v>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C990" t="n">
+        <v>14</v>
+      </c>
+      <c r="D990" t="n">
+        <v>21</v>
+      </c>
+      <c r="E990" t="n">
+        <v>35</v>
+      </c>
+      <c r="F990" t="n">
+        <v>37</v>
+      </c>
+      <c r="G990" t="n">
+        <v>49</v>
+      </c>
+      <c r="H990" t="n">
+        <v>1</v>
+      </c>
+      <c r="I990" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -31140,7 +31171,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.64</v>
+        <v>11.63</v>
       </c>
     </row>
     <row r="3">
@@ -31151,7 +31182,7 @@
         <v>114</v>
       </c>
       <c r="C3" t="n">
-        <v>11.54</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="4">
@@ -31159,10 +31190,10 @@
         <v>35</v>
       </c>
       <c r="B4" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>11.44</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="5">
@@ -31173,7 +31204,7 @@
         <v>112</v>
       </c>
       <c r="C5" t="n">
-        <v>11.34</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="6">
@@ -31181,10 +31212,10 @@
         <v>21</v>
       </c>
       <c r="B6" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>11.13</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="7">
@@ -31195,7 +31226,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.13</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="8">
@@ -31206,29 +31237,29 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>11.03</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B9" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>10.83</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="B10" t="n">
         <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="11">
@@ -31239,7 +31270,7 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.73</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="12">
@@ -31250,7 +31281,7 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>10.73</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="13">
@@ -31261,7 +31292,7 @@
         <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>10.63</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="14">
@@ -31272,7 +31303,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.63</v>
+        <v>10.62</v>
       </c>
     </row>
     <row r="15">
@@ -31283,29 +31314,29 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.53</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
       <c r="B16" t="n">
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.53</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="B17" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.43</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="18">
@@ -31316,18 +31347,18 @@
         <v>103</v>
       </c>
       <c r="C18" t="n">
-        <v>10.43</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B19" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C19" t="n">
-        <v>10.22</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="20">
@@ -31338,40 +31369,40 @@
         <v>101</v>
       </c>
       <c r="C20" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="B21" t="n">
         <v>101</v>
       </c>
       <c r="C21" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B22" t="n">
         <v>101</v>
       </c>
       <c r="C22" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B23" t="n">
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="24">
@@ -31382,7 +31413,7 @@
         <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="25">
@@ -31393,7 +31424,7 @@
         <v>99</v>
       </c>
       <c r="C25" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="26">
@@ -31404,7 +31435,7 @@
         <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="27">
@@ -31415,7 +31446,7 @@
         <v>99</v>
       </c>
       <c r="C27" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="28">
@@ -31426,7 +31457,7 @@
         <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>9.92</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="29">
@@ -31437,7 +31468,7 @@
         <v>98</v>
       </c>
       <c r="C29" t="n">
-        <v>9.92</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="30">
@@ -31448,7 +31479,7 @@
         <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="31">
@@ -31459,7 +31490,7 @@
         <v>97</v>
       </c>
       <c r="C31" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="32">
@@ -31470,7 +31501,7 @@
         <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -31481,7 +31512,7 @@
         <v>96</v>
       </c>
       <c r="C33" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -31492,7 +31523,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -31503,7 +31534,7 @@
         <v>94</v>
       </c>
       <c r="C35" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="36">
@@ -31514,7 +31545,7 @@
         <v>94</v>
       </c>
       <c r="C36" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="37">
@@ -31525,7 +31556,7 @@
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="38">
@@ -31536,7 +31567,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="39">
@@ -31547,7 +31578,7 @@
         <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="40">
@@ -31558,7 +31589,7 @@
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="41">
@@ -31569,7 +31600,7 @@
         <v>92</v>
       </c>
       <c r="C41" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -31580,7 +31611,7 @@
         <v>91</v>
       </c>
       <c r="C42" t="n">
-        <v>9.210000000000001</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -31591,7 +31622,7 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="44">
@@ -31602,7 +31633,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="45">
@@ -31613,7 +31644,7 @@
         <v>89</v>
       </c>
       <c r="C45" t="n">
-        <v>9.01</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
@@ -31624,7 +31655,7 @@
         <v>88</v>
       </c>
       <c r="C46" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="47">
@@ -31635,7 +31666,7 @@
         <v>88</v>
       </c>
       <c r="C47" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="48">
@@ -31646,7 +31677,7 @@
         <v>87</v>
       </c>
       <c r="C48" t="n">
-        <v>8.81</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -31657,7 +31688,7 @@
         <v>87</v>
       </c>
       <c r="C49" t="n">
-        <v>8.81</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -31679,7 +31710,7 @@
         <v>79</v>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
     </row>
   </sheetData>
@@ -31721,7 +31752,7 @@
         <v>212</v>
       </c>
       <c r="C2" t="n">
-        <v>21.46</v>
+        <v>21.44</v>
       </c>
     </row>
     <row r="3">
@@ -31732,7 +31763,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.55</v>
+        <v>20.53</v>
       </c>
     </row>
     <row r="4">
@@ -31743,7 +31774,7 @@
         <v>195</v>
       </c>
       <c r="C4" t="n">
-        <v>19.74</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="5">
@@ -31754,7 +31785,7 @@
         <v>192</v>
       </c>
       <c r="C5" t="n">
-        <v>19.43</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="6">
@@ -31765,7 +31796,7 @@
         <v>187</v>
       </c>
       <c r="C6" t="n">
-        <v>18.93</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="7">
@@ -31776,7 +31807,7 @@
         <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>18.52</v>
+        <v>18.5</v>
       </c>
     </row>
     <row r="8">
@@ -31784,10 +31815,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C8" t="n">
-        <v>18.12</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="9">
@@ -31798,7 +31829,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.9</v>
+        <v>16.89</v>
       </c>
     </row>
     <row r="10">
@@ -31809,7 +31840,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.5</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="11">
@@ -31820,7 +31851,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>14.88</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="12">
@@ -31828,10 +31859,10 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C12" t="n">
-        <v>8.4</v>
+        <v>8.49</v>
       </c>
     </row>
     <row r="13">
@@ -31842,7 +31873,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.58</v>
+        <v>6.57</v>
       </c>
     </row>
   </sheetData>
@@ -31884,7 +31915,7 @@
         <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>20.39</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="3">
@@ -31895,7 +31926,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.74</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="4">
@@ -31903,10 +31934,10 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>17.81</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="5">
@@ -31917,7 +31948,7 @@
         <v>80</v>
       </c>
       <c r="C5" t="n">
-        <v>17.17</v>
+        <v>17.13</v>
       </c>
     </row>
     <row r="6">
@@ -31925,10 +31956,10 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C6" t="n">
-        <v>16.74</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="7">
@@ -31939,7 +31970,7 @@
         <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>16.74</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="8">
@@ -31950,7 +31981,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.31</v>
+        <v>16.27</v>
       </c>
     </row>
     <row r="9">
@@ -31961,7 +31992,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>15.88</v>
+        <v>15.85</v>
       </c>
     </row>
     <row r="10">
@@ -31972,7 +32003,7 @@
         <v>72</v>
       </c>
       <c r="C10" t="n">
-        <v>15.45</v>
+        <v>15.42</v>
       </c>
     </row>
     <row r="11">
@@ -31983,7 +32014,7 @@
         <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>15.02</v>
+        <v>14.99</v>
       </c>
     </row>
     <row r="12">
@@ -31994,7 +32025,7 @@
         <v>69</v>
       </c>
       <c r="C12" t="n">
-        <v>14.81</v>
+        <v>14.78</v>
       </c>
     </row>
     <row r="13">
@@ -32005,7 +32036,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.95</v>
+        <v>13.92</v>
       </c>
     </row>
   </sheetData>
@@ -32501,13 +32532,13 @@
         <v>32</v>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
         <v>10.3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.19</v>
+        <v>3.29</v>
       </c>
     </row>
     <row r="3">
@@ -32515,13 +32546,13 @@
         <v>38</v>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
         <v>9.9</v>
       </c>
       <c r="D3" t="n">
-        <v>2.84</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="4">
@@ -32529,13 +32560,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
         <v>10.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="5">
@@ -32543,13 +32574,13 @@
         <v>18</v>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="6">
@@ -32557,13 +32588,13 @@
         <v>29</v>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
         <v>10.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="7">
@@ -32571,13 +32602,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>9.9</v>
       </c>
       <c r="D7" t="n">
-        <v>2.03</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="8">
@@ -32585,55 +32616,55 @@
         <v>44</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>10.4</v>
       </c>
       <c r="D8" t="n">
-        <v>1.92</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>8.9</v>
+        <v>9.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="D11" t="n">
-        <v>1.37</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="12">
@@ -32641,69 +32672,69 @@
         <v>20</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
         <v>8.4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="B13" t="n">
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>10.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>1.02</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>9.300000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="D14" t="n">
-        <v>1.19</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B15" t="n">
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>10.3</v>
+        <v>9.9</v>
       </c>
       <c r="D16" t="n">
-        <v>0.87</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="17">
@@ -32711,97 +32742,97 @@
         <v>13</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
         <v>9.5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B18" t="n">
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B19" t="n">
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>0.99</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.89</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="B21" t="n">
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B22" t="n">
         <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D22" t="n">
-        <v>0.79</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>9.4</v>
+        <v>11.3</v>
       </c>
       <c r="D23" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="24">
@@ -32809,318 +32840,318 @@
         <v>26</v>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" t="n">
         <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B25" t="n">
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.68</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B26" t="n">
         <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>11.3</v>
+        <v>10.9</v>
       </c>
       <c r="D26" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>9.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.61</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C28" t="n">
-        <v>10.6</v>
+        <v>10.1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B29" t="n">
         <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>10.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B30" t="n">
         <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>10.1</v>
+        <v>11.2</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>9.800000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="D31" t="n">
-        <v>0.51</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>0.45</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="D33" t="n">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B36" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C36" t="n">
-        <v>9.199999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="D36" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="B39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>9.199999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="D39" t="n">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="D40" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>8.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="D41" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B42" t="n">
         <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>9.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="D42" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="D43" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>10.4</v>
+        <v>11.3</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>10.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="D46" t="n">
         <v>0.09</v>
@@ -33142,13 +33173,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33156,13 +33187,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>11.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33170,13 +33201,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>11.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33184,13 +33215,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10.3</v>
+        <v>9.1</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I990"/>
+  <dimension ref="A1:I991"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31130,6 +31130,37 @@
       </c>
       <c r="I990" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C991" t="n">
+        <v>5</v>
+      </c>
+      <c r="D991" t="n">
+        <v>6</v>
+      </c>
+      <c r="E991" t="n">
+        <v>10</v>
+      </c>
+      <c r="F991" t="n">
+        <v>27</v>
+      </c>
+      <c r="G991" t="n">
+        <v>42</v>
+      </c>
+      <c r="H991" t="n">
+        <v>1</v>
+      </c>
+      <c r="I991" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -31171,7 +31202,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.63</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="3">
@@ -31182,7 +31213,7 @@
         <v>114</v>
       </c>
       <c r="C3" t="n">
-        <v>11.53</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="4">
@@ -31193,7 +31224,7 @@
         <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>11.53</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="5">
@@ -31204,7 +31235,7 @@
         <v>112</v>
       </c>
       <c r="C5" t="n">
-        <v>11.32</v>
+        <v>11.31</v>
       </c>
     </row>
     <row r="6">
@@ -31215,7 +31246,7 @@
         <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>11.22</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="7">
@@ -31226,7 +31257,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="8">
@@ -31237,7 +31268,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>11.02</v>
+        <v>11.01</v>
       </c>
     </row>
     <row r="9">
@@ -31248,7 +31279,7 @@
         <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>10.92</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="10">
@@ -31259,7 +31290,7 @@
         <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>10.82</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="11">
@@ -31270,7 +31301,7 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.72</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="12">
@@ -31281,7 +31312,7 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>10.72</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="13">
@@ -31292,7 +31323,7 @@
         <v>105</v>
       </c>
       <c r="C13" t="n">
-        <v>10.62</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="14">
@@ -31303,7 +31334,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.62</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="15">
@@ -31314,7 +31345,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.52</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="16">
@@ -31325,7 +31356,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.52</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="17">
@@ -31336,7 +31367,7 @@
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.52</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="18">
@@ -31347,7 +31378,7 @@
         <v>103</v>
       </c>
       <c r="C18" t="n">
-        <v>10.41</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="19">
@@ -31358,7 +31389,7 @@
         <v>102</v>
       </c>
       <c r="C19" t="n">
-        <v>10.31</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="20">
@@ -31369,7 +31400,7 @@
         <v>101</v>
       </c>
       <c r="C20" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="21">
@@ -31380,7 +31411,7 @@
         <v>101</v>
       </c>
       <c r="C21" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="22">
@@ -31391,7 +31422,7 @@
         <v>101</v>
       </c>
       <c r="C22" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="23">
@@ -31402,51 +31433,51 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B24" t="n">
         <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B25" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C25" t="n">
-        <v>10.01</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B26" t="n">
         <v>99</v>
       </c>
       <c r="C26" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B27" t="n">
         <v>99</v>
       </c>
       <c r="C27" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -31457,7 +31488,7 @@
         <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>9.91</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="29">
@@ -31468,7 +31499,7 @@
         <v>98</v>
       </c>
       <c r="C29" t="n">
-        <v>9.91</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="30">
@@ -31479,7 +31510,7 @@
         <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.81</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -31490,7 +31521,7 @@
         <v>97</v>
       </c>
       <c r="C31" t="n">
-        <v>9.81</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -31501,7 +31532,7 @@
         <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.710000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -31512,7 +31543,7 @@
         <v>96</v>
       </c>
       <c r="C33" t="n">
-        <v>9.710000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -31523,7 +31554,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.710000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -31534,7 +31565,7 @@
         <v>94</v>
       </c>
       <c r="C35" t="n">
-        <v>9.5</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="36">
@@ -31545,18 +31576,18 @@
         <v>94</v>
       </c>
       <c r="C36" t="n">
-        <v>9.5</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B37" t="n">
         <v>93</v>
       </c>
       <c r="C37" t="n">
-        <v>9.4</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -31567,7 +31598,7 @@
         <v>93</v>
       </c>
       <c r="C38" t="n">
-        <v>9.4</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -31578,18 +31609,18 @@
         <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.4</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="B40" t="n">
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.4</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -31597,10 +31628,10 @@
         <v>42</v>
       </c>
       <c r="B41" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>9.300000000000001</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -31608,43 +31639,43 @@
         <v>10</v>
       </c>
       <c r="B42" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B43" t="n">
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B44" t="n">
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="B45" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="46">
@@ -31652,10 +31683,10 @@
         <v>27</v>
       </c>
       <c r="B46" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.9</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="47">
@@ -31666,7 +31697,7 @@
         <v>88</v>
       </c>
       <c r="C47" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -31677,7 +31708,7 @@
         <v>87</v>
       </c>
       <c r="C48" t="n">
-        <v>8.800000000000001</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -31688,7 +31719,7 @@
         <v>87</v>
       </c>
       <c r="C49" t="n">
-        <v>8.800000000000001</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -31699,7 +31730,7 @@
         <v>86</v>
       </c>
       <c r="C50" t="n">
-        <v>8.699999999999999</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="51">
@@ -31710,7 +31741,7 @@
         <v>79</v>
       </c>
       <c r="C51" t="n">
-        <v>7.99</v>
+        <v>7.98</v>
       </c>
     </row>
   </sheetData>
@@ -31752,7 +31783,7 @@
         <v>212</v>
       </c>
       <c r="C2" t="n">
-        <v>21.44</v>
+        <v>21.41</v>
       </c>
     </row>
     <row r="3">
@@ -31763,7 +31794,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.53</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="4">
@@ -31771,10 +31802,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C4" t="n">
-        <v>19.72</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="5">
@@ -31785,7 +31816,7 @@
         <v>192</v>
       </c>
       <c r="C5" t="n">
-        <v>19.41</v>
+        <v>19.39</v>
       </c>
     </row>
     <row r="6">
@@ -31796,7 +31827,7 @@
         <v>187</v>
       </c>
       <c r="C6" t="n">
-        <v>18.91</v>
+        <v>18.89</v>
       </c>
     </row>
     <row r="7">
@@ -31807,7 +31838,7 @@
         <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>18.5</v>
+        <v>18.48</v>
       </c>
     </row>
     <row r="8">
@@ -31815,10 +31846,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C8" t="n">
-        <v>18.2</v>
+        <v>18.28</v>
       </c>
     </row>
     <row r="9">
@@ -31829,7 +31860,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.89</v>
+        <v>16.87</v>
       </c>
     </row>
     <row r="10">
@@ -31840,7 +31871,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.48</v>
+        <v>16.46</v>
       </c>
     </row>
     <row r="11">
@@ -31851,7 +31882,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>14.86</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="12">
@@ -31862,7 +31893,7 @@
         <v>84</v>
       </c>
       <c r="C12" t="n">
-        <v>8.49</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="13">
@@ -31915,7 +31946,7 @@
         <v>95</v>
       </c>
       <c r="C2" t="n">
-        <v>20.34</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="3">
@@ -31926,7 +31957,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.7</v>
+        <v>19.66</v>
       </c>
     </row>
     <row r="4">
@@ -31937,29 +31968,29 @@
         <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>17.99</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="B5" t="n">
         <v>80</v>
       </c>
       <c r="C5" t="n">
-        <v>17.13</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>16.92</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="7">
@@ -31970,7 +32001,7 @@
         <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>16.7</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="8">
@@ -31981,7 +32012,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.27</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="9">
@@ -31992,7 +32023,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>15.85</v>
+        <v>15.81</v>
       </c>
     </row>
     <row r="10">
@@ -32003,7 +32034,7 @@
         <v>72</v>
       </c>
       <c r="C10" t="n">
-        <v>15.42</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="11">
@@ -32014,7 +32045,7 @@
         <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>14.99</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="12">
@@ -32022,10 +32053,10 @@
         <v>8</v>
       </c>
       <c r="B12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.78</v>
+        <v>14.96</v>
       </c>
     </row>
     <row r="13">
@@ -32036,7 +32067,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.92</v>
+        <v>13.89</v>
       </c>
     </row>
   </sheetData>
@@ -32532,13 +32563,13 @@
         <v>32</v>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
         <v>10.3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.29</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="3">
@@ -32546,13 +32577,13 @@
         <v>38</v>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
         <v>9.9</v>
       </c>
       <c r="D3" t="n">
-        <v>2.94</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="4">
@@ -32560,13 +32591,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
         <v>10.1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="5">
@@ -32574,13 +32605,13 @@
         <v>18</v>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -32588,13 +32619,13 @@
         <v>29</v>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
         <v>10.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.48</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="7">
@@ -32602,13 +32633,13 @@
         <v>19</v>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
         <v>9.9</v>
       </c>
       <c r="D7" t="n">
-        <v>2.13</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="8">
@@ -32616,13 +32647,13 @@
         <v>44</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
         <v>10.4</v>
       </c>
       <c r="D8" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="9">
@@ -32630,13 +32661,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>9.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="10">
@@ -32644,111 +32675,111 @@
         <v>41</v>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>10.8</v>
+        <v>8.4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B12" t="n">
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B13" t="n">
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>10.3</v>
+        <v>9.1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.97</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>9.1</v>
+        <v>10.3</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B16" t="n">
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>9.9</v>
+        <v>10.2</v>
       </c>
       <c r="D16" t="n">
-        <v>1.01</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17" t="n">
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="18">
@@ -32756,38 +32787,38 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
         <v>9</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B19" t="n">
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>11.3</v>
       </c>
       <c r="D19" t="n">
-        <v>1.01</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B20" t="n">
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D20" t="n">
         <v>0.88</v>
@@ -32798,55 +32829,55 @@
         <v>30</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
         <v>9.4</v>
       </c>
       <c r="D21" t="n">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="D22" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B23" t="n">
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>11.3</v>
+        <v>10.1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B24" t="n">
         <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="D24" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="25">
@@ -32854,136 +32885,136 @@
         <v>15</v>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.71</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B26" t="n">
         <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>10.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>0.64</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B27" t="n">
         <v>7</v>
       </c>
       <c r="C27" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="D27" t="n">
-        <v>0.66</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="B29" t="n">
         <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="D29" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B30" t="n">
         <v>6</v>
       </c>
       <c r="C30" t="n">
-        <v>11.2</v>
+        <v>12.3</v>
       </c>
       <c r="D30" t="n">
-        <v>0.53</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="B32" t="n">
         <v>5</v>
       </c>
       <c r="C32" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D32" t="n">
-        <v>0.51</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B33" t="n">
         <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D34" t="n">
         <v>0.41</v>
@@ -32991,181 +33022,181 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
       </c>
       <c r="C35" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>0.43</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="B36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>9.5</v>
+        <v>10.6</v>
       </c>
       <c r="D36" t="n">
-        <v>0.42</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="D37" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B38" t="n">
         <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>9.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="D38" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>11.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="D41" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>10.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>11.3</v>
+        <v>9.1</v>
       </c>
       <c r="D44" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>11.6</v>
+        <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33173,13 +33204,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33187,13 +33218,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>9.800000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33201,13 +33232,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>8.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33215,13 +33246,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>9.1</v>
+        <v>10.6</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I991"/>
+  <dimension ref="A1:I992"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31161,6 +31161,37 @@
       </c>
       <c r="I991" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C992" t="n">
+        <v>4</v>
+      </c>
+      <c r="D992" t="n">
+        <v>25</v>
+      </c>
+      <c r="E992" t="n">
+        <v>30</v>
+      </c>
+      <c r="F992" t="n">
+        <v>32</v>
+      </c>
+      <c r="G992" t="n">
+        <v>33</v>
+      </c>
+      <c r="H992" t="n">
+        <v>4</v>
+      </c>
+      <c r="I992" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -31202,7 +31233,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.62</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="3">
@@ -31213,7 +31244,7 @@
         <v>114</v>
       </c>
       <c r="C3" t="n">
-        <v>11.52</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="4">
@@ -31224,7 +31255,7 @@
         <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>11.52</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="5">
@@ -31235,7 +31266,7 @@
         <v>112</v>
       </c>
       <c r="C5" t="n">
-        <v>11.31</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="6">
@@ -31246,7 +31277,7 @@
         <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>11.21</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="7">
@@ -31257,7 +31288,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="8">
@@ -31268,7 +31299,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>11.01</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -31279,7 +31310,7 @@
         <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>10.91</v>
+        <v>10.9</v>
       </c>
     </row>
     <row r="10">
@@ -31290,7 +31321,7 @@
         <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>10.81</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="11">
@@ -31301,7 +31332,7 @@
         <v>106</v>
       </c>
       <c r="C11" t="n">
-        <v>10.71</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="12">
@@ -31312,7 +31343,7 @@
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>10.71</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="13">
@@ -31320,10 +31351,10 @@
         <v>30</v>
       </c>
       <c r="B13" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C13" t="n">
-        <v>10.61</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="14">
@@ -31334,7 +31365,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.61</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="15">
@@ -31345,7 +31376,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.51</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="16">
@@ -31356,7 +31387,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.51</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="17">
@@ -31367,7 +31398,7 @@
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.51</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="18">
@@ -31378,7 +31409,7 @@
         <v>103</v>
       </c>
       <c r="C18" t="n">
-        <v>10.4</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="19">
@@ -31389,7 +31420,7 @@
         <v>102</v>
       </c>
       <c r="C19" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="20">
@@ -31400,7 +31431,7 @@
         <v>101</v>
       </c>
       <c r="C20" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="21">
@@ -31411,7 +31442,7 @@
         <v>101</v>
       </c>
       <c r="C21" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="22">
@@ -31422,7 +31453,7 @@
         <v>101</v>
       </c>
       <c r="C22" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="23">
@@ -31433,51 +31464,51 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B24" t="n">
         <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B25" t="n">
         <v>100</v>
       </c>
       <c r="C25" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B26" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B27" t="n">
         <v>99</v>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="28">
@@ -31488,7 +31519,7 @@
         <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>9.9</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -31499,7 +31530,7 @@
         <v>98</v>
       </c>
       <c r="C29" t="n">
-        <v>9.9</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -31510,7 +31541,7 @@
         <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -31521,7 +31552,7 @@
         <v>97</v>
       </c>
       <c r="C31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -31532,7 +31563,7 @@
         <v>96</v>
       </c>
       <c r="C32" t="n">
-        <v>9.699999999999999</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="33">
@@ -31543,7 +31574,7 @@
         <v>96</v>
       </c>
       <c r="C33" t="n">
-        <v>9.699999999999999</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="34">
@@ -31554,7 +31585,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.699999999999999</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="35">
@@ -31570,7 +31601,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B36" t="n">
         <v>94</v>
@@ -31581,46 +31612,46 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B37" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C37" t="n">
-        <v>9.390000000000001</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="B38" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C38" t="n">
-        <v>9.390000000000001</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="B39" t="n">
         <v>93</v>
       </c>
       <c r="C39" t="n">
-        <v>9.390000000000001</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="B40" t="n">
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.390000000000001</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -31631,7 +31662,7 @@
         <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>9.390000000000001</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -31642,7 +31673,7 @@
         <v>92</v>
       </c>
       <c r="C42" t="n">
-        <v>9.289999999999999</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -31653,7 +31684,7 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.09</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="44">
@@ -31664,7 +31695,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.09</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="45">
@@ -31675,7 +31706,7 @@
         <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>9.09</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="46">
@@ -31686,40 +31717,40 @@
         <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.99</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="B47" t="n">
         <v>88</v>
       </c>
       <c r="C47" t="n">
-        <v>8.890000000000001</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C48" t="n">
-        <v>8.789999999999999</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B49" t="n">
         <v>87</v>
       </c>
       <c r="C49" t="n">
-        <v>8.789999999999999</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -31730,7 +31761,7 @@
         <v>86</v>
       </c>
       <c r="C50" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="51">
@@ -31741,7 +31772,7 @@
         <v>79</v>
       </c>
       <c r="C51" t="n">
-        <v>7.98</v>
+        <v>7.97</v>
       </c>
     </row>
   </sheetData>
@@ -31780,10 +31811,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C2" t="n">
-        <v>21.41</v>
+        <v>21.49</v>
       </c>
     </row>
     <row r="3">
@@ -31794,7 +31825,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.51</v>
+        <v>20.48</v>
       </c>
     </row>
     <row r="4">
@@ -31805,7 +31836,7 @@
         <v>196</v>
       </c>
       <c r="C4" t="n">
-        <v>19.8</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="5">
@@ -31816,7 +31847,7 @@
         <v>192</v>
       </c>
       <c r="C5" t="n">
-        <v>19.39</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="6">
@@ -31824,10 +31855,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C6" t="n">
-        <v>18.89</v>
+        <v>18.97</v>
       </c>
     </row>
     <row r="7">
@@ -31838,7 +31869,7 @@
         <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>18.48</v>
+        <v>18.47</v>
       </c>
     </row>
     <row r="8">
@@ -31849,7 +31880,7 @@
         <v>181</v>
       </c>
       <c r="C8" t="n">
-        <v>18.28</v>
+        <v>18.26</v>
       </c>
     </row>
     <row r="9">
@@ -31860,7 +31891,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.87</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="10">
@@ -31871,7 +31902,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.46</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="11">
@@ -31882,7 +31913,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>14.85</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="12">
@@ -31904,7 +31935,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.57</v>
+        <v>6.56</v>
       </c>
     </row>
   </sheetData>
@@ -31943,10 +31974,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C2" t="n">
-        <v>20.3</v>
+        <v>20.47</v>
       </c>
     </row>
     <row r="3">
@@ -31957,7 +31988,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.66</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="4">
@@ -31968,7 +31999,7 @@
         <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>17.95</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="5">
@@ -31979,7 +32010,7 @@
         <v>80</v>
       </c>
       <c r="C5" t="n">
-        <v>17.09</v>
+        <v>17.06</v>
       </c>
     </row>
     <row r="6">
@@ -31990,7 +32021,7 @@
         <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>17.09</v>
+        <v>17.06</v>
       </c>
     </row>
     <row r="7">
@@ -32001,7 +32032,7 @@
         <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>16.67</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="8">
@@ -32012,7 +32043,7 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.24</v>
+        <v>16.2</v>
       </c>
     </row>
     <row r="9">
@@ -32023,7 +32054,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>15.81</v>
+        <v>15.78</v>
       </c>
     </row>
     <row r="10">
@@ -32031,10 +32062,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C10" t="n">
-        <v>15.38</v>
+        <v>15.57</v>
       </c>
     </row>
     <row r="11">
@@ -32045,7 +32076,7 @@
         <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>14.96</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="12">
@@ -32056,7 +32087,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.96</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="13">
@@ -32067,7 +32098,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.89</v>
+        <v>13.86</v>
       </c>
     </row>
   </sheetData>
@@ -32560,114 +32591,114 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n">
-        <v>10.3</v>
+        <v>9.9</v>
       </c>
       <c r="D2" t="n">
-        <v>3.39</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
-        <v>9.9</v>
+        <v>10.1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.04</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>2.68</v>
+        <v>3.11</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="B5" t="n">
         <v>27</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10.1</v>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="B6" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
-        <v>10.1</v>
+        <v>9.9</v>
       </c>
       <c r="D6" t="n">
-        <v>2.58</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="D8" t="n">
-        <v>2.11</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>9.5</v>
+        <v>8.4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="10">
@@ -32675,55 +32706,55 @@
         <v>41</v>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>8.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B12" t="n">
         <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>8.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.38</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="D13" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="14">
@@ -32731,27 +32762,27 @@
         <v>1</v>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
         <v>9.1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="B15" t="n">
         <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>10.3</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>1.07</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="16">
@@ -32759,41 +32790,41 @@
         <v>12</v>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
         <v>10.2</v>
       </c>
       <c r="D16" t="n">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
         <v>11</v>
-      </c>
-      <c r="B17" t="n">
-        <v>10</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B18" t="n">
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>1.11</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="19">
@@ -32801,13 +32832,13 @@
         <v>28</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
         <v>11.3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="20">
@@ -32815,88 +32846,88 @@
         <v>40</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C20" t="n">
         <v>10.3</v>
       </c>
       <c r="D20" t="n">
-        <v>0.88</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B21" t="n">
         <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>9.4</v>
+        <v>10.1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n">
         <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="D22" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C23" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="B24" t="n">
         <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>10.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.74</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>9.800000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B26" t="n">
         <v>7</v>
@@ -32910,293 +32941,293 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="B27" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>11.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.62</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="B28" t="n">
         <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D28" t="n">
-        <v>0.61</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B29" t="n">
         <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="D30" t="n">
-        <v>0.49</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B31" t="n">
         <v>5</v>
       </c>
       <c r="C31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.53</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="B33" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>9.199999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D33" t="n">
-        <v>0.54</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>9.699999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>0.41</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="D35" t="n">
-        <v>0.36</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>10.6</v>
+        <v>11.6</v>
       </c>
       <c r="D36" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>10.1</v>
+        <v>9.1</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>10.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>0.29</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>47</v>
+        <v>14</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="D40" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>11.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>8.699999999999999</v>
+        <v>10.8</v>
       </c>
       <c r="D42" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="D43" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="D44" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>9.800000000000001</v>
+        <v>11.1</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9</v>
+        <v>10.6</v>
       </c>
       <c r="D46" t="n">
-        <v>0.11</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>10.8</v>
+        <v>9.9</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33204,13 +33235,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>9.9</v>
+        <v>10.5</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33218,13 +33249,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33232,13 +33263,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33246,13 +33277,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I992"/>
+  <dimension ref="A1:I993"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31191,6 +31191,37 @@
         <v>4</v>
       </c>
       <c r="I992" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C993" t="n">
+        <v>17</v>
+      </c>
+      <c r="D993" t="n">
+        <v>23</v>
+      </c>
+      <c r="E993" t="n">
+        <v>33</v>
+      </c>
+      <c r="F993" t="n">
+        <v>46</v>
+      </c>
+      <c r="G993" t="n">
+        <v>47</v>
+      </c>
+      <c r="H993" t="n">
+        <v>4</v>
+      </c>
+      <c r="I993" t="n">
         <v>5</v>
       </c>
     </row>
@@ -31233,7 +31264,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.6</v>
+        <v>11.59</v>
       </c>
     </row>
     <row r="3">
@@ -31244,7 +31275,7 @@
         <v>114</v>
       </c>
       <c r="C3" t="n">
-        <v>11.5</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="4">
@@ -31255,7 +31286,7 @@
         <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>11.5</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="5">
@@ -31263,10 +31294,10 @@
         <v>17</v>
       </c>
       <c r="B5" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C5" t="n">
-        <v>11.3</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="6">
@@ -31277,7 +31308,7 @@
         <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>11.2</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="7">
@@ -31288,7 +31319,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="8">
@@ -31299,7 +31330,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="9">
@@ -31310,40 +31341,40 @@
         <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>10.9</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>10.8</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C11" t="n">
-        <v>10.7</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B12" t="n">
         <v>106</v>
       </c>
       <c r="C12" t="n">
-        <v>10.7</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="13">
@@ -31354,7 +31385,7 @@
         <v>106</v>
       </c>
       <c r="C13" t="n">
-        <v>10.7</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="14">
@@ -31365,7 +31396,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.6</v>
+        <v>10.58</v>
       </c>
     </row>
     <row r="15">
@@ -31376,7 +31407,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.49</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="16">
@@ -31387,7 +31418,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.49</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="17">
@@ -31398,7 +31429,7 @@
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.49</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="18">
@@ -31409,29 +31440,29 @@
         <v>103</v>
       </c>
       <c r="C18" t="n">
-        <v>10.39</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B19" t="n">
         <v>102</v>
       </c>
       <c r="C19" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B20" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C20" t="n">
-        <v>10.19</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="21">
@@ -31442,18 +31473,18 @@
         <v>101</v>
       </c>
       <c r="C21" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B22" t="n">
         <v>101</v>
       </c>
       <c r="C22" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="23">
@@ -31464,7 +31495,7 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="24">
@@ -31475,7 +31506,7 @@
         <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="25">
@@ -31486,7 +31517,7 @@
         <v>100</v>
       </c>
       <c r="C25" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="26">
@@ -31497,7 +31528,7 @@
         <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="27">
@@ -31508,7 +31539,7 @@
         <v>99</v>
       </c>
       <c r="C27" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="28">
@@ -31519,7 +31550,7 @@
         <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -31530,18 +31561,18 @@
         <v>98</v>
       </c>
       <c r="C29" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B30" t="n">
         <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -31552,29 +31583,29 @@
         <v>97</v>
       </c>
       <c r="C31" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B32" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C32" t="n">
-        <v>9.69</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B33" t="n">
         <v>96</v>
       </c>
       <c r="C33" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="34">
@@ -31585,29 +31616,29 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.69</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>3</v>
+        <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C35" t="n">
-        <v>9.49</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B36" t="n">
         <v>94</v>
       </c>
       <c r="C36" t="n">
-        <v>9.49</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="37">
@@ -31618,18 +31649,18 @@
         <v>94</v>
       </c>
       <c r="C37" t="n">
-        <v>9.49</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="B38" t="n">
         <v>94</v>
       </c>
       <c r="C38" t="n">
-        <v>9.49</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="39">
@@ -31673,7 +31704,7 @@
         <v>92</v>
       </c>
       <c r="C42" t="n">
-        <v>9.279999999999999</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="43">
@@ -31684,7 +31715,7 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="44">
@@ -31695,7 +31726,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="45">
@@ -31706,7 +31737,7 @@
         <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="46">
@@ -31717,7 +31748,7 @@
         <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.98</v>
+        <v>8.970000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -31728,7 +31759,7 @@
         <v>88</v>
       </c>
       <c r="C47" t="n">
-        <v>8.880000000000001</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -31739,7 +31770,7 @@
         <v>88</v>
       </c>
       <c r="C48" t="n">
-        <v>8.880000000000001</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -31750,7 +31781,7 @@
         <v>87</v>
       </c>
       <c r="C49" t="n">
-        <v>8.779999999999999</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="50">
@@ -31761,7 +31792,7 @@
         <v>86</v>
       </c>
       <c r="C50" t="n">
-        <v>8.68</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="51">
@@ -31772,7 +31803,7 @@
         <v>79</v>
       </c>
       <c r="C51" t="n">
-        <v>7.97</v>
+        <v>7.96</v>
       </c>
     </row>
   </sheetData>
@@ -31811,10 +31842,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C2" t="n">
-        <v>21.49</v>
+        <v>21.57</v>
       </c>
     </row>
     <row r="3">
@@ -31825,7 +31856,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.48</v>
+        <v>20.46</v>
       </c>
     </row>
     <row r="4">
@@ -31836,7 +31867,7 @@
         <v>196</v>
       </c>
       <c r="C4" t="n">
-        <v>19.78</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="5">
@@ -31847,7 +31878,7 @@
         <v>192</v>
       </c>
       <c r="C5" t="n">
-        <v>19.37</v>
+        <v>19.35</v>
       </c>
     </row>
     <row r="6">
@@ -31855,10 +31886,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C6" t="n">
-        <v>18.97</v>
+        <v>19.05</v>
       </c>
     </row>
     <row r="7">
@@ -31869,7 +31900,7 @@
         <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>18.47</v>
+        <v>18.45</v>
       </c>
     </row>
     <row r="8">
@@ -31880,7 +31911,7 @@
         <v>181</v>
       </c>
       <c r="C8" t="n">
-        <v>18.26</v>
+        <v>18.25</v>
       </c>
     </row>
     <row r="9">
@@ -31891,7 +31922,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.85</v>
+        <v>16.83</v>
       </c>
     </row>
     <row r="10">
@@ -31902,7 +31933,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.45</v>
+        <v>16.43</v>
       </c>
     </row>
     <row r="11">
@@ -31913,7 +31944,7 @@
         <v>147</v>
       </c>
       <c r="C11" t="n">
-        <v>14.83</v>
+        <v>14.82</v>
       </c>
     </row>
     <row r="12">
@@ -31924,7 +31955,7 @@
         <v>84</v>
       </c>
       <c r="C12" t="n">
-        <v>8.48</v>
+        <v>8.470000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -31935,7 +31966,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.56</v>
+        <v>6.55</v>
       </c>
     </row>
   </sheetData>
@@ -31974,10 +32005,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C2" t="n">
-        <v>20.47</v>
+        <v>20.64</v>
       </c>
     </row>
     <row r="3">
@@ -31988,7 +32019,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.62</v>
+        <v>19.57</v>
       </c>
     </row>
     <row r="4">
@@ -31999,7 +32030,7 @@
         <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>17.91</v>
+        <v>17.87</v>
       </c>
     </row>
     <row r="5">
@@ -32010,7 +32041,7 @@
         <v>80</v>
       </c>
       <c r="C5" t="n">
-        <v>17.06</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="6">
@@ -32021,7 +32052,7 @@
         <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>17.06</v>
+        <v>17.02</v>
       </c>
     </row>
     <row r="7">
@@ -32032,7 +32063,7 @@
         <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>16.63</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="8">
@@ -32043,29 +32074,29 @@
         <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>16.2</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B9" t="n">
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>15.78</v>
+        <v>15.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C10" t="n">
-        <v>15.57</v>
+        <v>15.74</v>
       </c>
     </row>
     <row r="11">
@@ -32076,7 +32107,7 @@
         <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>14.93</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="12">
@@ -32087,7 +32118,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.93</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="13">
@@ -32098,7 +32129,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.86</v>
+        <v>13.83</v>
       </c>
     </row>
   </sheetData>
@@ -32594,13 +32625,13 @@
         <v>38</v>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
         <v>9.9</v>
       </c>
       <c r="D2" t="n">
-        <v>3.14</v>
+        <v>3.24</v>
       </c>
     </row>
     <row r="3">
@@ -32608,13 +32639,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C3" t="n">
         <v>10.1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="4">
@@ -32622,13 +32653,13 @@
         <v>18</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="5">
@@ -32636,13 +32667,13 @@
         <v>29</v>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
         <v>10.1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="6">
@@ -32650,13 +32681,13 @@
         <v>19</v>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>9.9</v>
       </c>
       <c r="D6" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="7">
@@ -32664,13 +32695,13 @@
         <v>44</v>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
         <v>10.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -32678,13 +32709,13 @@
         <v>8</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
         <v>9.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="9">
@@ -32692,13 +32723,13 @@
         <v>20</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>8.4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.67</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="10">
@@ -32706,27 +32737,27 @@
         <v>41</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="B11" t="n">
         <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="12">
@@ -32734,13 +32765,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>9.5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="13">
@@ -32748,69 +32779,69 @@
         <v>3</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
         <v>10.3</v>
       </c>
       <c r="D13" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B14" t="n">
         <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="D15" t="n">
-        <v>1.23</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" t="n">
         <v>12</v>
       </c>
-      <c r="B16" t="n">
-        <v>11</v>
-      </c>
       <c r="C16" t="n">
-        <v>10.2</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
-        <v>1.08</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B17" t="n">
         <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>11.3</v>
       </c>
       <c r="D17" t="n">
-        <v>1.22</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="18">
@@ -32818,41 +32849,41 @@
         <v>26</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.89</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B20" t="n">
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.97</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="21">
@@ -32860,13 +32891,13 @@
         <v>22</v>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" t="n">
         <v>10.1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.89</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="22">
@@ -32874,32 +32905,32 @@
         <v>24</v>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C22" t="n">
         <v>10.9</v>
       </c>
       <c r="D22" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>9.800000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="D23" t="n">
-        <v>0.91</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B24" t="n">
         <v>8</v>
@@ -32913,240 +32944,240 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B25" t="n">
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="B26" t="n">
         <v>7</v>
       </c>
       <c r="C26" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D26" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B27" t="n">
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="B28" t="n">
         <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>9.5</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>0.63</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>9.199999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="D29" t="n">
-        <v>0.65</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="D30" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>9.699999999999999</v>
+        <v>11.6</v>
       </c>
       <c r="D31" t="n">
-        <v>0.52</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>10.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.38</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D34" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>10.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.29</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>11.6</v>
+        <v>9</v>
       </c>
       <c r="D36" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>9.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>0.22</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>8.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="D38" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="D39" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>9.5</v>
+        <v>11.1</v>
       </c>
       <c r="D40" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>9.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="42">
@@ -33154,18 +33185,18 @@
         <v>10</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
         <v>10.8</v>
       </c>
       <c r="D42" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
@@ -33179,27 +33210,27 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>11.2</v>
+        <v>9.4</v>
       </c>
       <c r="D44" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="D45" t="n">
         <v>0.09</v>
@@ -33207,7 +33238,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
@@ -33221,13 +33252,13 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33241,7 +33272,7 @@
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>10.5</v>
+        <v>10.4</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33249,13 +33280,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>10.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33263,13 +33294,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33277,13 +33308,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I993"/>
+  <dimension ref="A1:I994"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31223,6 +31223,37 @@
       </c>
       <c r="I993" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C994" t="n">
+        <v>2</v>
+      </c>
+      <c r="D994" t="n">
+        <v>7</v>
+      </c>
+      <c r="E994" t="n">
+        <v>10</v>
+      </c>
+      <c r="F994" t="n">
+        <v>29</v>
+      </c>
+      <c r="G994" t="n">
+        <v>30</v>
+      </c>
+      <c r="H994" t="n">
+        <v>5</v>
+      </c>
+      <c r="I994" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -31264,7 +31295,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.59</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="3">
@@ -31275,7 +31306,7 @@
         <v>114</v>
       </c>
       <c r="C3" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="4">
@@ -31286,7 +31317,7 @@
         <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="5">
@@ -31297,7 +31328,7 @@
         <v>113</v>
       </c>
       <c r="C5" t="n">
-        <v>11.39</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="6">
@@ -31308,7 +31339,7 @@
         <v>111</v>
       </c>
       <c r="C6" t="n">
-        <v>11.19</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="7">
@@ -31319,7 +31350,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.09</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="8">
@@ -31330,7 +31361,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>10.99</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="9">
@@ -31341,7 +31372,7 @@
         <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>10.89</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="10">
@@ -31352,7 +31383,7 @@
         <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>10.79</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="11">
@@ -31363,29 +31394,29 @@
         <v>107</v>
       </c>
       <c r="C11" t="n">
-        <v>10.79</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B12" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C12" t="n">
-        <v>10.69</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B13" t="n">
         <v>106</v>
       </c>
       <c r="C13" t="n">
-        <v>10.69</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="14">
@@ -31396,7 +31427,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.58</v>
+        <v>10.57</v>
       </c>
     </row>
     <row r="15">
@@ -31407,7 +31438,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.48</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="16">
@@ -31418,7 +31449,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.48</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="17">
@@ -31429,7 +31460,7 @@
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.48</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="18">
@@ -31440,18 +31471,18 @@
         <v>103</v>
       </c>
       <c r="C18" t="n">
-        <v>10.38</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B19" t="n">
         <v>102</v>
       </c>
       <c r="C19" t="n">
-        <v>10.28</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="20">
@@ -31462,29 +31493,29 @@
         <v>102</v>
       </c>
       <c r="C20" t="n">
-        <v>10.28</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C21" t="n">
-        <v>10.18</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B22" t="n">
         <v>101</v>
       </c>
       <c r="C22" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="23">
@@ -31495,7 +31526,7 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="24">
@@ -31506,7 +31537,7 @@
         <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="25">
@@ -31517,7 +31548,7 @@
         <v>100</v>
       </c>
       <c r="C25" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="26">
@@ -31528,7 +31559,7 @@
         <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="27">
@@ -31539,7 +31570,7 @@
         <v>99</v>
       </c>
       <c r="C27" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -31550,7 +31581,7 @@
         <v>98</v>
       </c>
       <c r="C28" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -31561,18 +31592,18 @@
         <v>98</v>
       </c>
       <c r="C29" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="B30" t="n">
         <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="31">
@@ -31583,7 +31614,7 @@
         <v>97</v>
       </c>
       <c r="C31" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="32">
@@ -31594,18 +31625,18 @@
         <v>97</v>
       </c>
       <c r="C32" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B33" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C33" t="n">
-        <v>9.68</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="34">
@@ -31616,7 +31647,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.68</v>
+        <v>9.67</v>
       </c>
     </row>
     <row r="35">
@@ -31627,7 +31658,7 @@
         <v>95</v>
       </c>
       <c r="C35" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="36">
@@ -31638,7 +31669,7 @@
         <v>94</v>
       </c>
       <c r="C36" t="n">
-        <v>9.48</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -31649,7 +31680,7 @@
         <v>94</v>
       </c>
       <c r="C37" t="n">
-        <v>9.48</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -31660,7 +31691,7 @@
         <v>94</v>
       </c>
       <c r="C38" t="n">
-        <v>9.48</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -31668,10 +31699,10 @@
         <v>2</v>
       </c>
       <c r="B39" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C39" t="n">
-        <v>9.380000000000001</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -31682,29 +31713,29 @@
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.380000000000001</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="B41" t="n">
         <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>9.380000000000001</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="B42" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C42" t="n">
-        <v>9.27</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -31715,7 +31746,7 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.07</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="44">
@@ -31726,7 +31757,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.07</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="45">
@@ -31737,7 +31768,7 @@
         <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>9.07</v>
+        <v>9.06</v>
       </c>
     </row>
     <row r="46">
@@ -31748,7 +31779,7 @@
         <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.970000000000001</v>
+        <v>8.960000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -31759,7 +31790,7 @@
         <v>88</v>
       </c>
       <c r="C47" t="n">
-        <v>8.869999999999999</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -31770,7 +31801,7 @@
         <v>88</v>
       </c>
       <c r="C48" t="n">
-        <v>8.869999999999999</v>
+        <v>8.859999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -31781,7 +31812,7 @@
         <v>87</v>
       </c>
       <c r="C49" t="n">
-        <v>8.77</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="50">
@@ -31792,7 +31823,7 @@
         <v>86</v>
       </c>
       <c r="C50" t="n">
-        <v>8.67</v>
+        <v>8.66</v>
       </c>
     </row>
     <row r="51">
@@ -31842,10 +31873,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C2" t="n">
-        <v>21.57</v>
+        <v>21.65</v>
       </c>
     </row>
     <row r="3">
@@ -31856,7 +31887,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.46</v>
+        <v>20.44</v>
       </c>
     </row>
     <row r="4">
@@ -31867,7 +31898,7 @@
         <v>196</v>
       </c>
       <c r="C4" t="n">
-        <v>19.76</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="5">
@@ -31878,7 +31909,7 @@
         <v>192</v>
       </c>
       <c r="C5" t="n">
-        <v>19.35</v>
+        <v>19.34</v>
       </c>
     </row>
     <row r="6">
@@ -31889,7 +31920,7 @@
         <v>189</v>
       </c>
       <c r="C6" t="n">
-        <v>19.05</v>
+        <v>19.03</v>
       </c>
     </row>
     <row r="7">
@@ -31900,7 +31931,7 @@
         <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>18.45</v>
+        <v>18.43</v>
       </c>
     </row>
     <row r="8">
@@ -31911,7 +31942,7 @@
         <v>181</v>
       </c>
       <c r="C8" t="n">
-        <v>18.25</v>
+        <v>18.23</v>
       </c>
     </row>
     <row r="9">
@@ -31922,7 +31953,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.83</v>
+        <v>16.82</v>
       </c>
     </row>
     <row r="10">
@@ -31933,7 +31964,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.43</v>
+        <v>16.41</v>
       </c>
     </row>
     <row r="11">
@@ -31941,10 +31972,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C11" t="n">
-        <v>14.82</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="12">
@@ -31955,7 +31986,7 @@
         <v>84</v>
       </c>
       <c r="C12" t="n">
-        <v>8.470000000000001</v>
+        <v>8.460000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -32005,10 +32036,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C2" t="n">
-        <v>20.64</v>
+        <v>20.81</v>
       </c>
     </row>
     <row r="3">
@@ -32019,7 +32050,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.57</v>
+        <v>19.53</v>
       </c>
     </row>
     <row r="4">
@@ -32030,7 +32061,7 @@
         <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>17.87</v>
+        <v>17.83</v>
       </c>
     </row>
     <row r="5">
@@ -32041,7 +32072,7 @@
         <v>80</v>
       </c>
       <c r="C5" t="n">
-        <v>17.02</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="6">
@@ -32052,7 +32083,7 @@
         <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>17.02</v>
+        <v>16.99</v>
       </c>
     </row>
     <row r="7">
@@ -32063,7 +32094,7 @@
         <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>16.6</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="8">
@@ -32071,10 +32102,10 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>16.17</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="9">
@@ -32085,7 +32116,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>15.74</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="10">
@@ -32096,7 +32127,7 @@
         <v>74</v>
       </c>
       <c r="C10" t="n">
-        <v>15.74</v>
+        <v>15.71</v>
       </c>
     </row>
     <row r="11">
@@ -32107,7 +32138,7 @@
         <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>14.89</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="12">
@@ -32118,7 +32149,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.89</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="13">
@@ -32129,7 +32160,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.83</v>
+        <v>13.8</v>
       </c>
     </row>
   </sheetData>
@@ -32301,7 +32332,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>27 &amp; 41</t>
+          <t>2 &amp; 30</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -32311,7 +32342,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>35 &amp; 46</t>
+          <t>27 &amp; 41</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -32321,17 +32352,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>41 &amp; 45</t>
+          <t>35 &amp; 46</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>39 &amp; 47</t>
+          <t>41 &amp; 45</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -32341,7 +32372,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>15 &amp; 18</t>
+          <t>39 &amp; 47</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -32351,7 +32382,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>9 &amp; 20</t>
+          <t>15 &amp; 18</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -32361,7 +32392,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>20 &amp; 49</t>
+          <t>9 &amp; 20</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -32371,7 +32402,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>26 &amp; 49</t>
+          <t>20 &amp; 49</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -32381,7 +32412,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2 &amp; 21</t>
+          <t>26 &amp; 49</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -32391,7 +32422,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>11 &amp; 35</t>
+          <t>2 &amp; 21</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -32401,7 +32432,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>30 &amp; 43</t>
+          <t>11 &amp; 35</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -32625,125 +32656,125 @@
         <v>38</v>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
         <v>9.9</v>
       </c>
       <c r="D2" t="n">
-        <v>3.24</v>
+        <v>3.34</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C3" t="n">
-        <v>10.1</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>2.88</v>
+        <v>3.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="D4" t="n">
-        <v>3.22</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.78</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>10.4</v>
+        <v>8.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>8.4</v>
+        <v>9.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.79</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>9.300000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.62</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="11">
@@ -32751,41 +32782,41 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>9.1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="B13" t="n">
         <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="D13" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
     </row>
     <row r="14">
@@ -32793,335 +32824,335 @@
         <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B15" t="n">
         <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B16" t="n">
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>11.3</v>
       </c>
       <c r="D16" t="n">
-        <v>1.33</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B17" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" t="n">
         <v>11</v>
       </c>
-      <c r="C17" t="n">
-        <v>11.3</v>
-      </c>
       <c r="D17" t="n">
-        <v>0.98</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B18" t="n">
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B19" t="n">
         <v>11</v>
       </c>
       <c r="C19" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="D19" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>10.1</v>
+        <v>12.3</v>
       </c>
       <c r="D21" t="n">
-        <v>0.99</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>10.9</v>
+        <v>9.5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.92</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B23" t="n">
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>0.65</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B24" t="n">
         <v>7</v>
       </c>
-      <c r="B24" t="n">
-        <v>8</v>
-      </c>
       <c r="C24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B25" t="n">
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="D25" t="n">
-        <v>0.71</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="D26" t="n">
-        <v>0.74</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="B27" t="n">
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
       <c r="D29" t="n">
-        <v>0.48</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>10.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>11.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.35</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D33" t="n">
-        <v>0.32</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>9.1</v>
+        <v>9.5</v>
       </c>
       <c r="D34" t="n">
-        <v>0.33</v>
+        <v>0.42</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>8.699999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="D35" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>9</v>
+        <v>11.2</v>
       </c>
       <c r="D36" t="n">
-        <v>0.33</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>9.800000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="D37" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="38">
@@ -33129,136 +33160,136 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
         <v>10.6</v>
       </c>
       <c r="D38" t="n">
-        <v>0.19</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>9.9</v>
+        <v>11.2</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>11.1</v>
+        <v>9.9</v>
       </c>
       <c r="D40" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="D41" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>10</v>
+        <v>33</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>10.8</v>
+        <v>10.4</v>
       </c>
       <c r="D42" t="n">
-        <v>0.18</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>9.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="D45" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>10.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>8.699999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33266,13 +33297,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33280,13 +33311,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>9.199999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33294,13 +33325,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33308,13 +33339,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10.2</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I994"/>
+  <dimension ref="A1:I995"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31254,6 +31254,37 @@
       </c>
       <c r="I994" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C995" t="n">
+        <v>21</v>
+      </c>
+      <c r="D995" t="n">
+        <v>30</v>
+      </c>
+      <c r="E995" t="n">
+        <v>36</v>
+      </c>
+      <c r="F995" t="n">
+        <v>43</v>
+      </c>
+      <c r="G995" t="n">
+        <v>48</v>
+      </c>
+      <c r="H995" t="n">
+        <v>1</v>
+      </c>
+      <c r="I995" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -31295,7 +31326,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.58</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="3">
@@ -31306,7 +31337,7 @@
         <v>114</v>
       </c>
       <c r="C3" t="n">
-        <v>11.48</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="4">
@@ -31317,7 +31348,7 @@
         <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>11.48</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="5">
@@ -31328,7 +31359,7 @@
         <v>113</v>
       </c>
       <c r="C5" t="n">
-        <v>11.38</v>
+        <v>11.37</v>
       </c>
     </row>
     <row r="6">
@@ -31336,10 +31367,10 @@
         <v>21</v>
       </c>
       <c r="B6" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>11.18</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="7">
@@ -31350,7 +31381,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.08</v>
+        <v>11.07</v>
       </c>
     </row>
     <row r="8">
@@ -31361,7 +31392,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>10.98</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="9">
@@ -31372,18 +31403,18 @@
         <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>10.88</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>10.78</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="11">
@@ -31394,18 +31425,18 @@
         <v>107</v>
       </c>
       <c r="C11" t="n">
-        <v>10.78</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B12" t="n">
         <v>107</v>
       </c>
       <c r="C12" t="n">
-        <v>10.78</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="13">
@@ -31416,7 +31447,7 @@
         <v>106</v>
       </c>
       <c r="C13" t="n">
-        <v>10.67</v>
+        <v>10.66</v>
       </c>
     </row>
     <row r="14">
@@ -31427,7 +31458,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.57</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="15">
@@ -31438,7 +31469,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.47</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="16">
@@ -31449,7 +31480,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.47</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="17">
@@ -31460,7 +31491,7 @@
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.47</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="18">
@@ -31471,7 +31502,7 @@
         <v>103</v>
       </c>
       <c r="C18" t="n">
-        <v>10.37</v>
+        <v>10.36</v>
       </c>
     </row>
     <row r="19">
@@ -31482,7 +31513,7 @@
         <v>102</v>
       </c>
       <c r="C19" t="n">
-        <v>10.27</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="20">
@@ -31493,7 +31524,7 @@
         <v>102</v>
       </c>
       <c r="C20" t="n">
-        <v>10.27</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="21">
@@ -31504,7 +31535,7 @@
         <v>102</v>
       </c>
       <c r="C21" t="n">
-        <v>10.27</v>
+        <v>10.26</v>
       </c>
     </row>
     <row r="22">
@@ -31515,7 +31546,7 @@
         <v>101</v>
       </c>
       <c r="C22" t="n">
-        <v>10.17</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="23">
@@ -31526,7 +31557,7 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.17</v>
+        <v>10.16</v>
       </c>
     </row>
     <row r="24">
@@ -31537,7 +31568,7 @@
         <v>100</v>
       </c>
       <c r="C24" t="n">
-        <v>10.07</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="25">
@@ -31548,7 +31579,7 @@
         <v>100</v>
       </c>
       <c r="C25" t="n">
-        <v>10.07</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="26">
@@ -31559,29 +31590,29 @@
         <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>10.07</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B27" t="n">
         <v>99</v>
       </c>
       <c r="C27" t="n">
-        <v>9.970000000000001</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B28" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C28" t="n">
-        <v>9.869999999999999</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -31592,7 +31623,7 @@
         <v>98</v>
       </c>
       <c r="C29" t="n">
-        <v>9.869999999999999</v>
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -31603,7 +31634,7 @@
         <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="31">
@@ -31614,7 +31645,7 @@
         <v>97</v>
       </c>
       <c r="C31" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="32">
@@ -31625,7 +31656,7 @@
         <v>97</v>
       </c>
       <c r="C32" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="33">
@@ -31636,7 +31667,7 @@
         <v>97</v>
       </c>
       <c r="C33" t="n">
-        <v>9.77</v>
+        <v>9.76</v>
       </c>
     </row>
     <row r="34">
@@ -31647,7 +31678,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.67</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="35">
@@ -31658,7 +31689,7 @@
         <v>95</v>
       </c>
       <c r="C35" t="n">
-        <v>9.57</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="36">
@@ -31669,7 +31700,7 @@
         <v>94</v>
       </c>
       <c r="C36" t="n">
-        <v>9.470000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -31680,7 +31711,7 @@
         <v>94</v>
       </c>
       <c r="C37" t="n">
-        <v>9.470000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -31691,7 +31722,7 @@
         <v>94</v>
       </c>
       <c r="C38" t="n">
-        <v>9.470000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -31702,7 +31733,7 @@
         <v>94</v>
       </c>
       <c r="C39" t="n">
-        <v>9.470000000000001</v>
+        <v>9.460000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -31713,7 +31744,7 @@
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.369999999999999</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -31724,7 +31755,7 @@
         <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>9.369999999999999</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -31735,7 +31766,7 @@
         <v>93</v>
       </c>
       <c r="C42" t="n">
-        <v>9.369999999999999</v>
+        <v>9.359999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -31746,7 +31777,7 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.06</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="44">
@@ -31757,7 +31788,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.06</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -31768,7 +31799,7 @@
         <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>9.06</v>
+        <v>9.050000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -31779,7 +31810,7 @@
         <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.960000000000001</v>
+        <v>8.949999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -31790,7 +31821,7 @@
         <v>88</v>
       </c>
       <c r="C47" t="n">
-        <v>8.859999999999999</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="48">
@@ -31801,7 +31832,7 @@
         <v>88</v>
       </c>
       <c r="C48" t="n">
-        <v>8.859999999999999</v>
+        <v>8.85</v>
       </c>
     </row>
     <row r="49">
@@ -31812,7 +31843,7 @@
         <v>87</v>
       </c>
       <c r="C49" t="n">
-        <v>8.76</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="50">
@@ -31820,10 +31851,10 @@
         <v>36</v>
       </c>
       <c r="B50" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C50" t="n">
-        <v>8.66</v>
+        <v>8.75</v>
       </c>
     </row>
     <row r="51">
@@ -31831,10 +31862,10 @@
         <v>48</v>
       </c>
       <c r="B51" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C51" t="n">
-        <v>7.96</v>
+        <v>8.050000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -31873,10 +31904,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C2" t="n">
-        <v>21.65</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="3">
@@ -31887,7 +31918,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.44</v>
+        <v>20.42</v>
       </c>
     </row>
     <row r="4">
@@ -31898,7 +31929,7 @@
         <v>196</v>
       </c>
       <c r="C4" t="n">
-        <v>19.74</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="5">
@@ -31909,7 +31940,7 @@
         <v>192</v>
       </c>
       <c r="C5" t="n">
-        <v>19.34</v>
+        <v>19.32</v>
       </c>
     </row>
     <row r="6">
@@ -31920,7 +31951,7 @@
         <v>189</v>
       </c>
       <c r="C6" t="n">
-        <v>19.03</v>
+        <v>19.01</v>
       </c>
     </row>
     <row r="7">
@@ -31931,7 +31962,7 @@
         <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>18.43</v>
+        <v>18.41</v>
       </c>
     </row>
     <row r="8">
@@ -31939,10 +31970,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C8" t="n">
-        <v>18.23</v>
+        <v>18.31</v>
       </c>
     </row>
     <row r="9">
@@ -31953,7 +31984,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.82</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="10">
@@ -31964,7 +31995,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.41</v>
+        <v>16.4</v>
       </c>
     </row>
     <row r="11">
@@ -31975,7 +32006,7 @@
         <v>148</v>
       </c>
       <c r="C11" t="n">
-        <v>14.9</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="12">
@@ -31986,7 +32017,7 @@
         <v>84</v>
       </c>
       <c r="C12" t="n">
-        <v>8.460000000000001</v>
+        <v>8.449999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -31997,7 +32028,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.55</v>
+        <v>6.54</v>
       </c>
     </row>
   </sheetData>
@@ -32036,10 +32067,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>20.81</v>
+        <v>20.97</v>
       </c>
     </row>
     <row r="3">
@@ -32050,7 +32081,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.53</v>
+        <v>19.49</v>
       </c>
     </row>
     <row r="4">
@@ -32061,7 +32092,7 @@
         <v>84</v>
       </c>
       <c r="C4" t="n">
-        <v>17.83</v>
+        <v>17.8</v>
       </c>
     </row>
     <row r="5">
@@ -32069,10 +32100,10 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C5" t="n">
-        <v>16.99</v>
+        <v>17.16</v>
       </c>
     </row>
     <row r="6">
@@ -32083,7 +32114,7 @@
         <v>80</v>
       </c>
       <c r="C6" t="n">
-        <v>16.99</v>
+        <v>16.95</v>
       </c>
     </row>
     <row r="7">
@@ -32094,7 +32125,7 @@
         <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>16.56</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="8">
@@ -32105,7 +32136,7 @@
         <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>16.35</v>
+        <v>16.31</v>
       </c>
     </row>
     <row r="9">
@@ -32116,7 +32147,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>15.71</v>
+        <v>15.68</v>
       </c>
     </row>
     <row r="10">
@@ -32127,7 +32158,7 @@
         <v>74</v>
       </c>
       <c r="C10" t="n">
-        <v>15.71</v>
+        <v>15.68</v>
       </c>
     </row>
     <row r="11">
@@ -32138,7 +32169,7 @@
         <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>14.86</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="12">
@@ -32149,7 +32180,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.86</v>
+        <v>14.83</v>
       </c>
     </row>
     <row r="13">
@@ -32160,7 +32191,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.8</v>
+        <v>13.77</v>
       </c>
     </row>
   </sheetData>
@@ -32312,7 +32343,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6 &amp; 21</t>
+          <t>30 &amp; 43</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -32322,7 +32353,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1 &amp; 18</t>
+          <t>6 &amp; 21</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -32332,7 +32363,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2 &amp; 30</t>
+          <t>1 &amp; 18</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -32342,7 +32373,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>27 &amp; 41</t>
+          <t>2 &amp; 30</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -32352,7 +32383,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>35 &amp; 46</t>
+          <t>36 &amp; 43</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -32362,27 +32393,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>41 &amp; 45</t>
+          <t>27 &amp; 41</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>39 &amp; 47</t>
+          <t>35 &amp; 46</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15 &amp; 18</t>
+          <t>41 &amp; 45</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -32392,7 +32423,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>9 &amp; 20</t>
+          <t>39 &amp; 47</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -32402,7 +32433,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>20 &amp; 49</t>
+          <t>15 &amp; 18</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -32412,7 +32443,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>26 &amp; 49</t>
+          <t>9 &amp; 20</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -32422,7 +32453,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2 &amp; 21</t>
+          <t>20 &amp; 49</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -32432,7 +32463,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>11 &amp; 35</t>
+          <t>26 &amp; 49</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -32656,13 +32687,13 @@
         <v>38</v>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
         <v>9.9</v>
       </c>
       <c r="D2" t="n">
-        <v>3.34</v>
+        <v>3.45</v>
       </c>
     </row>
     <row r="3">
@@ -32670,13 +32701,13 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>3.33</v>
+        <v>3.44</v>
       </c>
     </row>
     <row r="4">
@@ -32684,13 +32715,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
         <v>9.9</v>
       </c>
       <c r="D4" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="5">
@@ -32698,13 +32729,13 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
         <v>10.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="6">
@@ -32712,13 +32743,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>9.5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="7">
@@ -32726,13 +32757,13 @@
         <v>20</v>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
         <v>8.4</v>
       </c>
       <c r="D7" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
     </row>
     <row r="8">
@@ -32740,13 +32771,13 @@
         <v>41</v>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
     </row>
     <row r="9">
@@ -32754,13 +32785,13 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>9.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
     </row>
     <row r="10">
@@ -32768,13 +32799,13 @@
         <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>10.3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="11">
@@ -32782,13 +32813,13 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
         <v>9.1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="12">
@@ -32796,13 +32827,13 @@
         <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="13">
@@ -32810,13 +32841,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
         <v>10.2</v>
       </c>
       <c r="D13" t="n">
-        <v>1.28</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="14">
@@ -32824,13 +32855,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>1.45</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="15">
@@ -32838,13 +32869,13 @@
         <v>40</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>10.3</v>
       </c>
       <c r="D15" t="n">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="16">
@@ -32852,13 +32883,13 @@
         <v>28</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
         <v>11.3</v>
       </c>
       <c r="D16" t="n">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="17">
@@ -32866,13 +32897,13 @@
         <v>26</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="18">
@@ -32880,13 +32911,13 @@
         <v>15</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
     </row>
     <row r="19">
@@ -32894,13 +32925,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C19" t="n">
         <v>10.9</v>
       </c>
       <c r="D19" t="n">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="20">
@@ -32908,139 +32939,139 @@
         <v>22</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C20" t="n">
         <v>10.1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.09</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B21" t="n">
         <v>9</v>
       </c>
       <c r="C21" t="n">
-        <v>12.3</v>
+        <v>9.5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.73</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>9.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B23" t="n">
         <v>8</v>
       </c>
       <c r="C23" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>9.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B25" t="n">
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>10.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>10.1</v>
+        <v>9.5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.57</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>11.6</v>
+        <v>9.1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.43</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="30">
@@ -33048,150 +33079,150 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.46</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>9.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="D31" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.44</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>9</v>
+        <v>9.9</v>
       </c>
       <c r="D33" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>9.5</v>
+        <v>11.2</v>
       </c>
       <c r="D34" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>11.1</v>
+        <v>9.9</v>
       </c>
       <c r="D35" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="D36" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>9.9</v>
+        <v>11.2</v>
       </c>
       <c r="D37" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>10.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>11.2</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D40" t="n">
         <v>0.2</v>
@@ -33199,16 +33230,16 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="D41" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="42">
@@ -33216,32 +33247,32 @@
         <v>33</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
         <v>10.4</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>8.699999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="D43" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
@@ -33255,41 +33286,41 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="D46" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>10.3</v>
+        <v>8.9</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33297,13 +33328,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33311,13 +33342,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>10.7</v>
+        <v>11.5</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33325,13 +33356,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33339,13 +33370,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>30</v>
+        <v>48</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>9.300000000000001</v>
+        <v>12.3</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I995"/>
+  <dimension ref="A1:I996"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31285,6 +31285,37 @@
       </c>
       <c r="I995" t="n">
         <v>5</v>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C996" t="n">
+        <v>4</v>
+      </c>
+      <c r="D996" t="n">
+        <v>6</v>
+      </c>
+      <c r="E996" t="n">
+        <v>7</v>
+      </c>
+      <c r="F996" t="n">
+        <v>17</v>
+      </c>
+      <c r="G996" t="n">
+        <v>45</v>
+      </c>
+      <c r="H996" t="n">
+        <v>7</v>
+      </c>
+      <c r="I996" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -31326,40 +31357,40 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.57</v>
+        <v>11.56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B3" t="n">
         <v>114</v>
       </c>
       <c r="C3" t="n">
-        <v>11.47</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" t="n">
         <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>11.47</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B5" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C5" t="n">
-        <v>11.37</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="6">
@@ -31370,7 +31401,7 @@
         <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>11.27</v>
+        <v>11.26</v>
       </c>
     </row>
     <row r="7">
@@ -31381,7 +31412,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.07</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="8">
@@ -31392,7 +31423,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>10.97</v>
+        <v>10.95</v>
       </c>
     </row>
     <row r="9">
@@ -31403,7 +31434,7 @@
         <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>10.87</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="10">
@@ -31414,7 +31445,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>10.87</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="11">
@@ -31425,7 +31456,7 @@
         <v>107</v>
       </c>
       <c r="C11" t="n">
-        <v>10.76</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="12">
@@ -31436,7 +31467,7 @@
         <v>107</v>
       </c>
       <c r="C12" t="n">
-        <v>10.76</v>
+        <v>10.75</v>
       </c>
     </row>
     <row r="13">
@@ -31447,7 +31478,7 @@
         <v>106</v>
       </c>
       <c r="C13" t="n">
-        <v>10.66</v>
+        <v>10.65</v>
       </c>
     </row>
     <row r="14">
@@ -31458,7 +31489,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.56</v>
+        <v>10.55</v>
       </c>
     </row>
     <row r="15">
@@ -31469,7 +31500,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.46</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="16">
@@ -31480,7 +31511,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.46</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="17">
@@ -31491,73 +31522,73 @@
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.46</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B18" t="n">
         <v>103</v>
       </c>
       <c r="C18" t="n">
-        <v>10.36</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B19" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C19" t="n">
-        <v>10.26</v>
+        <v>10.35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B20" t="n">
         <v>102</v>
       </c>
       <c r="C20" t="n">
-        <v>10.26</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B21" t="n">
         <v>102</v>
       </c>
       <c r="C21" t="n">
-        <v>10.26</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="B22" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C22" t="n">
-        <v>10.16</v>
+        <v>10.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B23" t="n">
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.16</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="24">
@@ -31565,21 +31596,21 @@
         <v>4</v>
       </c>
       <c r="B24" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C24" t="n">
-        <v>10.06</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B25" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C25" t="n">
-        <v>10.06</v>
+        <v>10.15</v>
       </c>
     </row>
     <row r="26">
@@ -31590,7 +31621,7 @@
         <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>10.06</v>
+        <v>10.05</v>
       </c>
     </row>
     <row r="27">
@@ -31601,7 +31632,7 @@
         <v>99</v>
       </c>
       <c r="C27" t="n">
-        <v>9.960000000000001</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="28">
@@ -31612,7 +31643,7 @@
         <v>99</v>
       </c>
       <c r="C28" t="n">
-        <v>9.960000000000001</v>
+        <v>9.949999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -31623,7 +31654,7 @@
         <v>98</v>
       </c>
       <c r="C29" t="n">
-        <v>9.859999999999999</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="30">
@@ -31634,7 +31665,7 @@
         <v>97</v>
       </c>
       <c r="C30" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="31">
@@ -31645,7 +31676,7 @@
         <v>97</v>
       </c>
       <c r="C31" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="32">
@@ -31656,7 +31687,7 @@
         <v>97</v>
       </c>
       <c r="C32" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="33">
@@ -31667,7 +31698,7 @@
         <v>97</v>
       </c>
       <c r="C33" t="n">
-        <v>9.76</v>
+        <v>9.75</v>
       </c>
     </row>
     <row r="34">
@@ -31678,7 +31709,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.66</v>
+        <v>9.65</v>
       </c>
     </row>
     <row r="35">
@@ -31689,7 +31720,7 @@
         <v>95</v>
       </c>
       <c r="C35" t="n">
-        <v>9.56</v>
+        <v>9.550000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -31700,7 +31731,7 @@
         <v>94</v>
       </c>
       <c r="C36" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -31711,7 +31742,7 @@
         <v>94</v>
       </c>
       <c r="C37" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -31722,7 +31753,7 @@
         <v>94</v>
       </c>
       <c r="C38" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -31733,7 +31764,7 @@
         <v>94</v>
       </c>
       <c r="C39" t="n">
-        <v>9.460000000000001</v>
+        <v>9.449999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -31744,7 +31775,7 @@
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="41">
@@ -31755,7 +31786,7 @@
         <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="42">
@@ -31766,7 +31797,7 @@
         <v>93</v>
       </c>
       <c r="C42" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
     </row>
     <row r="43">
@@ -31810,7 +31841,7 @@
         <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.949999999999999</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="47">
@@ -31821,7 +31852,7 @@
         <v>88</v>
       </c>
       <c r="C47" t="n">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="48">
@@ -31832,7 +31863,7 @@
         <v>88</v>
       </c>
       <c r="C48" t="n">
-        <v>8.85</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="49">
@@ -31843,7 +31874,7 @@
         <v>87</v>
       </c>
       <c r="C49" t="n">
-        <v>8.75</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="50">
@@ -31854,7 +31885,7 @@
         <v>87</v>
       </c>
       <c r="C50" t="n">
-        <v>8.75</v>
+        <v>8.74</v>
       </c>
     </row>
     <row r="51">
@@ -31865,7 +31896,7 @@
         <v>80</v>
       </c>
       <c r="C51" t="n">
-        <v>8.050000000000001</v>
+        <v>8.039999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -31907,7 +31938,7 @@
         <v>216</v>
       </c>
       <c r="C2" t="n">
-        <v>21.73</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="3">
@@ -31918,7 +31949,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.42</v>
+        <v>20.4</v>
       </c>
     </row>
     <row r="4">
@@ -31929,7 +31960,7 @@
         <v>196</v>
       </c>
       <c r="C4" t="n">
-        <v>19.72</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="5">
@@ -31937,10 +31968,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>19.32</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="6">
@@ -31951,7 +31982,7 @@
         <v>189</v>
       </c>
       <c r="C6" t="n">
-        <v>19.01</v>
+        <v>18.99</v>
       </c>
     </row>
     <row r="7">
@@ -31962,7 +31993,7 @@
         <v>183</v>
       </c>
       <c r="C7" t="n">
-        <v>18.41</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="8">
@@ -31973,7 +32004,7 @@
         <v>182</v>
       </c>
       <c r="C8" t="n">
-        <v>18.31</v>
+        <v>18.29</v>
       </c>
     </row>
     <row r="9">
@@ -31984,7 +32015,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.8</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="10">
@@ -31995,7 +32026,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.4</v>
+        <v>16.38</v>
       </c>
     </row>
     <row r="11">
@@ -32006,7 +32037,7 @@
         <v>148</v>
       </c>
       <c r="C11" t="n">
-        <v>14.89</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="12">
@@ -32014,10 +32045,10 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" t="n">
-        <v>8.449999999999999</v>
+        <v>8.539999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -32028,7 +32059,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.54</v>
+        <v>6.53</v>
       </c>
     </row>
   </sheetData>
@@ -32070,7 +32101,7 @@
         <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>20.97</v>
+        <v>20.93</v>
       </c>
     </row>
     <row r="3">
@@ -32081,7 +32112,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.49</v>
+        <v>19.45</v>
       </c>
     </row>
     <row r="4">
@@ -32089,10 +32120,10 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" t="n">
-        <v>17.8</v>
+        <v>17.97</v>
       </c>
     </row>
     <row r="5">
@@ -32103,7 +32134,7 @@
         <v>81</v>
       </c>
       <c r="C5" t="n">
-        <v>17.16</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="6">
@@ -32111,10 +32142,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C6" t="n">
-        <v>16.95</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="7">
@@ -32125,7 +32156,7 @@
         <v>78</v>
       </c>
       <c r="C7" t="n">
-        <v>16.53</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="8">
@@ -32136,7 +32167,7 @@
         <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>16.31</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="9">
@@ -32147,7 +32178,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>15.68</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="10">
@@ -32158,7 +32189,7 @@
         <v>74</v>
       </c>
       <c r="C10" t="n">
-        <v>15.68</v>
+        <v>15.64</v>
       </c>
     </row>
     <row r="11">
@@ -32169,7 +32200,7 @@
         <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>14.83</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="12">
@@ -32180,7 +32211,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.83</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="13">
@@ -32191,7 +32222,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.77</v>
+        <v>13.74</v>
       </c>
     </row>
   </sheetData>
@@ -32687,13 +32718,13 @@
         <v>38</v>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
         <v>9.9</v>
       </c>
       <c r="D2" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="3">
@@ -32701,13 +32732,13 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>3.44</v>
+        <v>3.56</v>
       </c>
     </row>
     <row r="4">
@@ -32715,13 +32746,13 @@
         <v>19</v>
       </c>
       <c r="B4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="n">
         <v>9.9</v>
       </c>
       <c r="D4" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="5">
@@ -32729,13 +32760,13 @@
         <v>44</v>
       </c>
       <c r="B5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n">
         <v>10.4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.49</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="6">
@@ -32743,13 +32774,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
         <v>9.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.01</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="7">
@@ -32757,13 +32788,13 @@
         <v>20</v>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>8.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="8">
@@ -32771,13 +32802,13 @@
         <v>41</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>1.84</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="9">
@@ -32785,13 +32816,13 @@
         <v>13</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
         <v>9.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="10">
@@ -32799,13 +32830,13 @@
         <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>10.3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.46</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="11">
@@ -32813,13 +32844,13 @@
         <v>1</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>9.1</v>
       </c>
       <c r="D11" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="12">
@@ -32827,13 +32858,13 @@
         <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="13">
@@ -32841,13 +32872,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
         <v>10.2</v>
       </c>
       <c r="D13" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="14">
@@ -32855,13 +32886,13 @@
         <v>11</v>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="15">
@@ -32869,13 +32900,13 @@
         <v>40</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>10.3</v>
       </c>
       <c r="D15" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="16">
@@ -32883,13 +32914,13 @@
         <v>28</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
         <v>11.3</v>
       </c>
       <c r="D16" t="n">
-        <v>1.15</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="17">
@@ -32897,13 +32928,13 @@
         <v>26</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>1.18</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="18">
@@ -32911,13 +32942,13 @@
         <v>15</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="19">
@@ -32925,13 +32956,13 @@
         <v>24</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
         <v>10.9</v>
       </c>
       <c r="D19" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="20">
@@ -32939,13 +32970,13 @@
         <v>22</v>
       </c>
       <c r="B20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C20" t="n">
         <v>10.1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="21">
@@ -32953,83 +32984,83 @@
         <v>39</v>
       </c>
       <c r="B21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C21" t="n">
         <v>9.5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B22" t="n">
         <v>9</v>
       </c>
       <c r="C22" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
+        <v>50</v>
+      </c>
+      <c r="B23" t="n">
         <v>9</v>
       </c>
-      <c r="B23" t="n">
-        <v>8</v>
-      </c>
       <c r="C23" t="n">
-        <v>9.699999999999999</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
-        <v>0.83</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="B24" t="n">
         <v>8</v>
       </c>
       <c r="C24" t="n">
-        <v>11</v>
+        <v>10.4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.73</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B25" t="n">
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>10.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="27">
@@ -33037,55 +33068,55 @@
         <v>14</v>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" t="n">
         <v>9.5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.53</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.51</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>9.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>0.55</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>8.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="D30" t="n">
-        <v>0.58</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="31">
@@ -33093,13 +33124,13 @@
         <v>42</v>
       </c>
       <c r="B31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C31" t="n">
         <v>10.6</v>
       </c>
       <c r="D31" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="32">
@@ -33107,32 +33138,32 @@
         <v>5</v>
       </c>
       <c r="B32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C32" t="n">
         <v>11.1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>6</v>
+        <v>32</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>9.9</v>
+        <v>10.6</v>
       </c>
       <c r="D33" t="n">
-        <v>0.41</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
@@ -33146,181 +33177,181 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>9.9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>10.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="D37" t="n">
-        <v>0.27</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="B38" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C38" t="n">
-        <v>9.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="D38" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>8.699999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="D39" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>9.800000000000001</v>
+        <v>10.7</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>10.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>0.19</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>10.3</v>
+        <v>8.9</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>10.7</v>
+        <v>10.1</v>
       </c>
       <c r="D45" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>8.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33328,13 +33359,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33342,13 +33373,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33356,13 +33387,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>43</v>
+        <v>6</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>10.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33370,13 +33401,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I996"/>
+  <dimension ref="A1:I997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31316,6 +31316,37 @@
       </c>
       <c r="I996" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="997">
+      <c r="A997" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C997" t="n">
+        <v>7</v>
+      </c>
+      <c r="D997" t="n">
+        <v>12</v>
+      </c>
+      <c r="E997" t="n">
+        <v>19</v>
+      </c>
+      <c r="F997" t="n">
+        <v>28</v>
+      </c>
+      <c r="G997" t="n">
+        <v>50</v>
+      </c>
+      <c r="H997" t="n">
+        <v>1</v>
+      </c>
+      <c r="I997" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -31357,7 +31388,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.56</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="3">
@@ -31368,7 +31399,7 @@
         <v>114</v>
       </c>
       <c r="C3" t="n">
-        <v>11.46</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="4">
@@ -31379,7 +31410,7 @@
         <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>11.46</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="5">
@@ -31390,7 +31421,7 @@
         <v>114</v>
       </c>
       <c r="C5" t="n">
-        <v>11.46</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="6">
@@ -31401,7 +31432,7 @@
         <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>11.26</v>
+        <v>11.24</v>
       </c>
     </row>
     <row r="7">
@@ -31412,7 +31443,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.06</v>
+        <v>11.04</v>
       </c>
     </row>
     <row r="8">
@@ -31423,7 +31454,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>10.95</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="9">
@@ -31434,7 +31465,7 @@
         <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>10.85</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="10">
@@ -31445,7 +31476,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>10.85</v>
+        <v>10.84</v>
       </c>
     </row>
     <row r="11">
@@ -31456,7 +31487,7 @@
         <v>107</v>
       </c>
       <c r="C11" t="n">
-        <v>10.75</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="12">
@@ -31467,7 +31498,7 @@
         <v>107</v>
       </c>
       <c r="C12" t="n">
-        <v>10.75</v>
+        <v>10.74</v>
       </c>
     </row>
     <row r="13">
@@ -31478,7 +31509,7 @@
         <v>106</v>
       </c>
       <c r="C13" t="n">
-        <v>10.65</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="14">
@@ -31489,7 +31520,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.55</v>
+        <v>10.54</v>
       </c>
     </row>
     <row r="15">
@@ -31500,7 +31531,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.45</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="16">
@@ -31511,29 +31542,29 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.45</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="B17" t="n">
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.45</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="B18" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C18" t="n">
-        <v>10.35</v>
+        <v>10.44</v>
       </c>
     </row>
     <row r="19">
@@ -31544,7 +31575,7 @@
         <v>103</v>
       </c>
       <c r="C19" t="n">
-        <v>10.35</v>
+        <v>10.34</v>
       </c>
     </row>
     <row r="20">
@@ -31555,7 +31586,7 @@
         <v>102</v>
       </c>
       <c r="C20" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="21">
@@ -31566,7 +31597,7 @@
         <v>102</v>
       </c>
       <c r="C21" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="22">
@@ -31577,7 +31608,7 @@
         <v>102</v>
       </c>
       <c r="C22" t="n">
-        <v>10.25</v>
+        <v>10.24</v>
       </c>
     </row>
     <row r="23">
@@ -31588,7 +31619,7 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.15</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="24">
@@ -31599,7 +31630,7 @@
         <v>101</v>
       </c>
       <c r="C24" t="n">
-        <v>10.15</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="25">
@@ -31610,62 +31641,62 @@
         <v>101</v>
       </c>
       <c r="C25" t="n">
-        <v>10.15</v>
+        <v>10.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B26" t="n">
         <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>10.05</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>43</v>
+        <v>15</v>
       </c>
       <c r="B27" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C27" t="n">
-        <v>9.949999999999999</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B28" t="n">
         <v>99</v>
       </c>
       <c r="C28" t="n">
-        <v>9.949999999999999</v>
+        <v>9.94</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B29" t="n">
         <v>98</v>
       </c>
       <c r="C29" t="n">
-        <v>9.85</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B30" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C30" t="n">
-        <v>9.75</v>
+        <v>9.84</v>
       </c>
     </row>
     <row r="31">
@@ -31676,18 +31707,18 @@
         <v>97</v>
       </c>
       <c r="C31" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B32" t="n">
         <v>97</v>
       </c>
       <c r="C32" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="33">
@@ -31698,7 +31729,7 @@
         <v>97</v>
       </c>
       <c r="C33" t="n">
-        <v>9.75</v>
+        <v>9.74</v>
       </c>
     </row>
     <row r="34">
@@ -31709,7 +31740,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.65</v>
+        <v>9.640000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -31720,7 +31751,7 @@
         <v>95</v>
       </c>
       <c r="C35" t="n">
-        <v>9.550000000000001</v>
+        <v>9.539999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -31731,7 +31762,7 @@
         <v>94</v>
       </c>
       <c r="C36" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="37">
@@ -31742,7 +31773,7 @@
         <v>94</v>
       </c>
       <c r="C37" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="38">
@@ -31753,7 +31784,7 @@
         <v>94</v>
       </c>
       <c r="C38" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="39">
@@ -31764,7 +31795,7 @@
         <v>94</v>
       </c>
       <c r="C39" t="n">
-        <v>9.449999999999999</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="40">
@@ -31775,7 +31806,7 @@
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.35</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="41">
@@ -31786,7 +31817,7 @@
         <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>9.35</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="42">
@@ -31797,7 +31828,7 @@
         <v>93</v>
       </c>
       <c r="C42" t="n">
-        <v>9.35</v>
+        <v>9.34</v>
       </c>
     </row>
     <row r="43">
@@ -31808,7 +31839,7 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.050000000000001</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -31819,7 +31850,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.050000000000001</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -31830,7 +31861,7 @@
         <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>9.050000000000001</v>
+        <v>9.039999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -31846,18 +31877,18 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C47" t="n">
-        <v>8.84</v>
+        <v>8.94</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="B48" t="n">
         <v>88</v>
@@ -31868,13 +31899,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B49" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C49" t="n">
-        <v>8.74</v>
+        <v>8.84</v>
       </c>
     </row>
     <row r="50">
@@ -31885,7 +31916,7 @@
         <v>87</v>
       </c>
       <c r="C50" t="n">
-        <v>8.74</v>
+        <v>8.73</v>
       </c>
     </row>
     <row r="51">
@@ -31896,7 +31927,7 @@
         <v>80</v>
       </c>
       <c r="C51" t="n">
-        <v>8.039999999999999</v>
+        <v>8.029999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -31938,7 +31969,7 @@
         <v>216</v>
       </c>
       <c r="C2" t="n">
-        <v>21.71</v>
+        <v>21.69</v>
       </c>
     </row>
     <row r="3">
@@ -31949,7 +31980,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.4</v>
+        <v>20.38</v>
       </c>
     </row>
     <row r="4">
@@ -31960,7 +31991,7 @@
         <v>196</v>
       </c>
       <c r="C4" t="n">
-        <v>19.7</v>
+        <v>19.68</v>
       </c>
     </row>
     <row r="5">
@@ -31971,7 +32002,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>19.4</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="6">
@@ -31982,7 +32013,7 @@
         <v>189</v>
       </c>
       <c r="C6" t="n">
-        <v>18.99</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="7">
@@ -31990,10 +32021,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>18.39</v>
+        <v>18.47</v>
       </c>
     </row>
     <row r="8">
@@ -32001,10 +32032,10 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C8" t="n">
-        <v>18.29</v>
+        <v>18.37</v>
       </c>
     </row>
     <row r="9">
@@ -32015,7 +32046,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.78</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="10">
@@ -32026,7 +32057,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.38</v>
+        <v>16.37</v>
       </c>
     </row>
     <row r="11">
@@ -32037,7 +32068,7 @@
         <v>148</v>
       </c>
       <c r="C11" t="n">
-        <v>14.87</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="12">
@@ -32048,7 +32079,7 @@
         <v>85</v>
       </c>
       <c r="C12" t="n">
-        <v>8.539999999999999</v>
+        <v>8.529999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -32101,7 +32132,7 @@
         <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>20.93</v>
+        <v>20.89</v>
       </c>
     </row>
     <row r="3">
@@ -32112,7 +32143,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.45</v>
+        <v>19.41</v>
       </c>
     </row>
     <row r="4">
@@ -32123,7 +32154,7 @@
         <v>85</v>
       </c>
       <c r="C4" t="n">
-        <v>17.97</v>
+        <v>17.93</v>
       </c>
     </row>
     <row r="5">
@@ -32131,10 +32162,10 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C5" t="n">
-        <v>17.12</v>
+        <v>17.3</v>
       </c>
     </row>
     <row r="6">
@@ -32145,7 +32176,7 @@
         <v>81</v>
       </c>
       <c r="C6" t="n">
-        <v>17.12</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="7">
@@ -32153,10 +32184,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>16.49</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="8">
@@ -32167,7 +32198,7 @@
         <v>77</v>
       </c>
       <c r="C8" t="n">
-        <v>16.28</v>
+        <v>16.24</v>
       </c>
     </row>
     <row r="9">
@@ -32178,7 +32209,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>15.64</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="10">
@@ -32189,7 +32220,7 @@
         <v>74</v>
       </c>
       <c r="C10" t="n">
-        <v>15.64</v>
+        <v>15.61</v>
       </c>
     </row>
     <row r="11">
@@ -32200,7 +32231,7 @@
         <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>14.8</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="12">
@@ -32211,7 +32242,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.8</v>
+        <v>14.77</v>
       </c>
     </row>
     <row r="13">
@@ -32222,7 +32253,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.74</v>
+        <v>13.71</v>
       </c>
     </row>
   </sheetData>
@@ -32444,7 +32475,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>41 &amp; 45</t>
+          <t>7 &amp; 19</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -32454,7 +32485,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>39 &amp; 47</t>
+          <t>41 &amp; 45</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -32464,7 +32495,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>15 &amp; 18</t>
+          <t>39 &amp; 47</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -32474,7 +32505,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>9 &amp; 20</t>
+          <t>15 &amp; 18</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -32484,7 +32515,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>20 &amp; 49</t>
+          <t>9 &amp; 20</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -32494,7 +32525,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>26 &amp; 49</t>
+          <t>20 &amp; 49</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -32718,13 +32749,13 @@
         <v>38</v>
       </c>
       <c r="B2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C2" t="n">
         <v>9.9</v>
       </c>
       <c r="D2" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="3">
@@ -32732,55 +32763,55 @@
         <v>18</v>
       </c>
       <c r="B3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>3.56</v>
+        <v>3.67</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="B4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C4" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.74</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="B5" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.59</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>8</v>
+        <v>41</v>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="7">
@@ -32788,41 +32819,41 @@
         <v>20</v>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
         <v>8.4</v>
       </c>
       <c r="D7" t="n">
-        <v>2.15</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D8" t="n">
-        <v>1.94</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="10">
@@ -32830,27 +32861,27 @@
         <v>3</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
         <v>10.3</v>
       </c>
       <c r="D10" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B11" t="n">
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="12">
@@ -32858,419 +32889,419 @@
         <v>16</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B13" t="n">
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D13" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B14" t="n">
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>1.68</v>
+        <v>1.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B15" t="n">
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="D15" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B16" t="n">
         <v>14</v>
       </c>
       <c r="C16" t="n">
-        <v>11.3</v>
+        <v>10.1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.24</v>
+        <v>1.39</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B17" t="n">
         <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D18" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>10.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>1.2</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B20" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="D20" t="n">
-        <v>1.29</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>1.05</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B22" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="D22" t="n">
-        <v>0.93</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B23" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>0.82</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.77</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B25" t="n">
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>9.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="D26" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B27" t="n">
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>9.5</v>
+        <v>11.1</v>
       </c>
       <c r="D27" t="n">
-        <v>0.63</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B28" t="n">
         <v>6</v>
       </c>
       <c r="C28" t="n">
-        <v>9.1</v>
+        <v>10.6</v>
       </c>
       <c r="D28" t="n">
-        <v>0.66</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>8.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="D30" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="B31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>10.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.47</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B32" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="D32" t="n">
-        <v>0.45</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>10.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
       </c>
       <c r="C34" t="n">
-        <v>11.2</v>
+        <v>10.2</v>
       </c>
       <c r="D34" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="D35" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="D36" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="D37" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>10.2</v>
+        <v>12.3</v>
       </c>
       <c r="D38" t="n">
-        <v>0.29</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>10.3</v>
+        <v>11.5</v>
       </c>
       <c r="D39" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>10.7</v>
+        <v>8.9</v>
       </c>
       <c r="D40" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>10.3</v>
+        <v>10.1</v>
       </c>
       <c r="D41" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="42">
@@ -33278,69 +33309,69 @@
         <v>30</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>10.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
@@ -33359,13 +33390,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>8.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33373,13 +33404,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33387,13 +33418,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33401,13 +33432,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I997"/>
+  <dimension ref="A1:I998"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31347,6 +31347,37 @@
       </c>
       <c r="I997" t="n">
         <v>6</v>
+      </c>
+    </row>
+    <row r="998">
+      <c r="A998" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C998" t="n">
+        <v>18</v>
+      </c>
+      <c r="D998" t="n">
+        <v>38</v>
+      </c>
+      <c r="E998" t="n">
+        <v>41</v>
+      </c>
+      <c r="F998" t="n">
+        <v>43</v>
+      </c>
+      <c r="G998" t="n">
+        <v>46</v>
+      </c>
+      <c r="H998" t="n">
+        <v>7</v>
+      </c>
+      <c r="I998" t="n">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -31388,7 +31419,7 @@
         <v>115</v>
       </c>
       <c r="C2" t="n">
-        <v>11.55</v>
+        <v>11.53</v>
       </c>
     </row>
     <row r="3">
@@ -31399,7 +31430,7 @@
         <v>114</v>
       </c>
       <c r="C3" t="n">
-        <v>11.45</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="4">
@@ -31410,7 +31441,7 @@
         <v>114</v>
       </c>
       <c r="C4" t="n">
-        <v>11.45</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="5">
@@ -31421,7 +31452,7 @@
         <v>114</v>
       </c>
       <c r="C5" t="n">
-        <v>11.45</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="6">
@@ -31432,7 +31463,7 @@
         <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>11.24</v>
+        <v>11.23</v>
       </c>
     </row>
     <row r="7">
@@ -31443,7 +31474,7 @@
         <v>110</v>
       </c>
       <c r="C7" t="n">
-        <v>11.04</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="8">
@@ -31454,18 +31485,18 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>10.94</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="B9" t="n">
         <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>10.84</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="10">
@@ -31476,40 +31507,40 @@
         <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>10.84</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="B11" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C11" t="n">
-        <v>10.74</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B12" t="n">
         <v>107</v>
       </c>
       <c r="C12" t="n">
-        <v>10.74</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>41</v>
+        <v>23</v>
       </c>
       <c r="B13" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C13" t="n">
-        <v>10.64</v>
+        <v>10.73</v>
       </c>
     </row>
     <row r="14">
@@ -31520,7 +31551,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.54</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="15">
@@ -31531,7 +31562,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.44</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="16">
@@ -31542,7 +31573,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.44</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="17">
@@ -31553,7 +31584,7 @@
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.44</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="18">
@@ -31564,7 +31595,7 @@
         <v>104</v>
       </c>
       <c r="C18" t="n">
-        <v>10.44</v>
+        <v>10.43</v>
       </c>
     </row>
     <row r="19">
@@ -31575,40 +31606,40 @@
         <v>103</v>
       </c>
       <c r="C19" t="n">
-        <v>10.34</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B20" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C20" t="n">
-        <v>10.24</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B21" t="n">
         <v>102</v>
       </c>
       <c r="C21" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B22" t="n">
         <v>102</v>
       </c>
       <c r="C22" t="n">
-        <v>10.24</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="23">
@@ -31619,7 +31650,7 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.14</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="24">
@@ -31630,7 +31661,7 @@
         <v>101</v>
       </c>
       <c r="C24" t="n">
-        <v>10.14</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="25">
@@ -31641,18 +31672,18 @@
         <v>101</v>
       </c>
       <c r="C25" t="n">
-        <v>10.14</v>
+        <v>10.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B26" t="n">
         <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>10.04</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="27">
@@ -31663,40 +31694,40 @@
         <v>100</v>
       </c>
       <c r="C27" t="n">
-        <v>10.04</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="B28" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C28" t="n">
-        <v>9.94</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B29" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C29" t="n">
-        <v>9.84</v>
+        <v>9.93</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B30" t="n">
         <v>98</v>
       </c>
       <c r="C30" t="n">
-        <v>9.84</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="31">
@@ -31707,7 +31738,7 @@
         <v>97</v>
       </c>
       <c r="C31" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="32">
@@ -31718,7 +31749,7 @@
         <v>97</v>
       </c>
       <c r="C32" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="33">
@@ -31729,7 +31760,7 @@
         <v>97</v>
       </c>
       <c r="C33" t="n">
-        <v>9.74</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="34">
@@ -31740,7 +31771,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.640000000000001</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -31751,7 +31782,7 @@
         <v>95</v>
       </c>
       <c r="C35" t="n">
-        <v>9.539999999999999</v>
+        <v>9.529999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -31762,7 +31793,7 @@
         <v>94</v>
       </c>
       <c r="C36" t="n">
-        <v>9.44</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="37">
@@ -31773,7 +31804,7 @@
         <v>94</v>
       </c>
       <c r="C37" t="n">
-        <v>9.44</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="38">
@@ -31784,7 +31815,7 @@
         <v>94</v>
       </c>
       <c r="C38" t="n">
-        <v>9.44</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="39">
@@ -31795,7 +31826,7 @@
         <v>94</v>
       </c>
       <c r="C39" t="n">
-        <v>9.44</v>
+        <v>9.43</v>
       </c>
     </row>
     <row r="40">
@@ -31806,7 +31837,7 @@
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.34</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="41">
@@ -31817,7 +31848,7 @@
         <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>9.34</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="42">
@@ -31828,7 +31859,7 @@
         <v>93</v>
       </c>
       <c r="C42" t="n">
-        <v>9.34</v>
+        <v>9.33</v>
       </c>
     </row>
     <row r="43">
@@ -31839,7 +31870,7 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.039999999999999</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -31850,7 +31881,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.039999999999999</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -31861,7 +31892,7 @@
         <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>9.039999999999999</v>
+        <v>9.029999999999999</v>
       </c>
     </row>
     <row r="46">
@@ -31872,7 +31903,7 @@
         <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.94</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="47">
@@ -31883,7 +31914,7 @@
         <v>89</v>
       </c>
       <c r="C47" t="n">
-        <v>8.94</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="48">
@@ -31894,7 +31925,7 @@
         <v>88</v>
       </c>
       <c r="C48" t="n">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="49">
@@ -31905,7 +31936,7 @@
         <v>88</v>
       </c>
       <c r="C49" t="n">
-        <v>8.84</v>
+        <v>8.83</v>
       </c>
     </row>
     <row r="50">
@@ -31927,7 +31958,7 @@
         <v>80</v>
       </c>
       <c r="C51" t="n">
-        <v>8.029999999999999</v>
+        <v>8.02</v>
       </c>
     </row>
   </sheetData>
@@ -31969,7 +32000,7 @@
         <v>216</v>
       </c>
       <c r="C2" t="n">
-        <v>21.69</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="3">
@@ -31980,7 +32011,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.38</v>
+        <v>20.36</v>
       </c>
     </row>
     <row r="4">
@@ -31991,7 +32022,7 @@
         <v>196</v>
       </c>
       <c r="C4" t="n">
-        <v>19.68</v>
+        <v>19.66</v>
       </c>
     </row>
     <row r="5">
@@ -31999,10 +32030,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C5" t="n">
-        <v>19.38</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="6">
@@ -32013,7 +32044,7 @@
         <v>189</v>
       </c>
       <c r="C6" t="n">
-        <v>18.98</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="7">
@@ -32024,7 +32055,7 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>18.47</v>
+        <v>18.46</v>
       </c>
     </row>
     <row r="8">
@@ -32035,7 +32066,7 @@
         <v>183</v>
       </c>
       <c r="C8" t="n">
-        <v>18.37</v>
+        <v>18.36</v>
       </c>
     </row>
     <row r="9">
@@ -32046,7 +32077,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.77</v>
+        <v>16.75</v>
       </c>
     </row>
     <row r="10">
@@ -32057,7 +32088,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.37</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="11">
@@ -32065,10 +32096,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C11" t="n">
-        <v>14.86</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="12">
@@ -32090,7 +32121,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
     </row>
   </sheetData>
@@ -32132,7 +32163,7 @@
         <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>20.89</v>
+        <v>20.84</v>
       </c>
     </row>
     <row r="3">
@@ -32143,7 +32174,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.41</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="4">
@@ -32154,7 +32185,7 @@
         <v>85</v>
       </c>
       <c r="C4" t="n">
-        <v>17.93</v>
+        <v>17.89</v>
       </c>
     </row>
     <row r="5">
@@ -32165,7 +32196,7 @@
         <v>82</v>
       </c>
       <c r="C5" t="n">
-        <v>17.3</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="6">
@@ -32173,10 +32204,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C6" t="n">
-        <v>17.09</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="7">
@@ -32187,7 +32218,7 @@
         <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>16.67</v>
+        <v>16.63</v>
       </c>
     </row>
     <row r="8">
@@ -32195,10 +32226,10 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>16.24</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="9">
@@ -32209,7 +32240,7 @@
         <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>15.61</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="10">
@@ -32220,7 +32251,7 @@
         <v>74</v>
       </c>
       <c r="C10" t="n">
-        <v>15.61</v>
+        <v>15.58</v>
       </c>
     </row>
     <row r="11">
@@ -32231,7 +32262,7 @@
         <v>70</v>
       </c>
       <c r="C11" t="n">
-        <v>14.77</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="12">
@@ -32242,7 +32273,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.77</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="13">
@@ -32253,7 +32284,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.71</v>
+        <v>13.68</v>
       </c>
     </row>
   </sheetData>
@@ -32746,273 +32777,273 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C2" t="n">
-        <v>9.9</v>
+        <v>10.4</v>
       </c>
       <c r="D2" t="n">
-        <v>3.65</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>9.5</v>
       </c>
       <c r="D3" t="n">
-        <v>3.67</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="B4" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
-        <v>10.4</v>
+        <v>8.4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.69</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.22</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>9.300000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D6" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
       <c r="D7" t="n">
-        <v>2.27</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B8" t="n">
         <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
-        <v>1.78</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B9" t="n">
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>10.3</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B11" t="n">
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="D11" t="n">
-        <v>1.79</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1.77</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B13" t="n">
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>10.3</v>
+        <v>10.9</v>
       </c>
       <c r="D13" t="n">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B14" t="n">
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>10.1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>10.9</v>
+        <v>9.5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>1.39</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>9.800000000000001</v>
+        <v>10.4</v>
       </c>
       <c r="D17" t="n">
-        <v>1.42</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="D19" t="n">
-        <v>1.03</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" t="n">
         <v>8</v>
@@ -33026,83 +33057,83 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="B22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C22" t="n">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="D22" t="n">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B23" t="n">
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>8.699999999999999</v>
+        <v>11.1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B24" t="n">
         <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>9.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="D24" t="n">
-        <v>0.72</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B25" t="n">
         <v>7</v>
       </c>
       <c r="C25" t="n">
-        <v>9.1</v>
+        <v>10.6</v>
       </c>
       <c r="D25" t="n">
-        <v>0.77</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="D26" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="B27" t="n">
         <v>6</v>
       </c>
       <c r="C27" t="n">
-        <v>11.1</v>
+        <v>11.2</v>
       </c>
       <c r="D27" t="n">
         <v>0.54</v>
@@ -33110,223 +33141,223 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>11.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>0.45</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B30" t="n">
         <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="D30" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>46</v>
+        <v>29</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>9.800000000000001</v>
+        <v>10.3</v>
       </c>
       <c r="D31" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="D32" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>9.199999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="D33" t="n">
-        <v>0.44</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>10.2</v>
+        <v>11.5</v>
       </c>
       <c r="D34" t="n">
-        <v>0.39</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="D35" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>10.3</v>
+        <v>8.9</v>
       </c>
       <c r="D36" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>10.7</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>10.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B42" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>9.199999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>0.22</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="D43" t="n">
         <v>0.1</v>
@@ -33334,55 +33365,55 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>9.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="D45" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33390,13 +33421,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33404,13 +33435,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33418,13 +33449,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>11.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33432,13 +33463,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I998"/>
+  <dimension ref="A1:I999"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31378,6 +31378,37 @@
       </c>
       <c r="I998" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C999" t="n">
+        <v>11</v>
+      </c>
+      <c r="D999" t="n">
+        <v>17</v>
+      </c>
+      <c r="E999" t="n">
+        <v>20</v>
+      </c>
+      <c r="F999" t="n">
+        <v>22</v>
+      </c>
+      <c r="G999" t="n">
+        <v>35</v>
+      </c>
+      <c r="H999" t="n">
+        <v>4</v>
+      </c>
+      <c r="I999" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -31416,10 +31447,10 @@
         <v>20</v>
       </c>
       <c r="B2" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C2" t="n">
-        <v>11.53</v>
+        <v>11.62</v>
       </c>
     </row>
     <row r="3">
@@ -31427,32 +31458,32 @@
         <v>17</v>
       </c>
       <c r="B3" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C3" t="n">
-        <v>11.43</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C4" t="n">
-        <v>11.43</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B5" t="n">
         <v>114</v>
       </c>
       <c r="C5" t="n">
-        <v>11.43</v>
+        <v>11.42</v>
       </c>
     </row>
     <row r="6">
@@ -31463,7 +31494,7 @@
         <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>11.23</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="7">
@@ -31471,10 +31502,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>11.03</v>
+        <v>11.12</v>
       </c>
     </row>
     <row r="8">
@@ -31485,7 +31516,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>10.93</v>
+        <v>10.92</v>
       </c>
     </row>
     <row r="9">
@@ -31496,7 +31527,7 @@
         <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="10">
@@ -31507,7 +31538,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="11">
@@ -31518,7 +31549,7 @@
         <v>108</v>
       </c>
       <c r="C11" t="n">
-        <v>10.83</v>
+        <v>10.82</v>
       </c>
     </row>
     <row r="12">
@@ -31529,7 +31560,7 @@
         <v>107</v>
       </c>
       <c r="C12" t="n">
-        <v>10.73</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="13">
@@ -31540,7 +31571,7 @@
         <v>107</v>
       </c>
       <c r="C13" t="n">
-        <v>10.73</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="14">
@@ -31551,7 +31582,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.53</v>
+        <v>10.52</v>
       </c>
     </row>
     <row r="15">
@@ -31562,7 +31593,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="16">
@@ -31573,7 +31604,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="17">
@@ -31584,7 +31615,7 @@
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="18">
@@ -31595,7 +31626,7 @@
         <v>104</v>
       </c>
       <c r="C18" t="n">
-        <v>10.43</v>
+        <v>10.42</v>
       </c>
     </row>
     <row r="19">
@@ -31606,7 +31637,7 @@
         <v>103</v>
       </c>
       <c r="C19" t="n">
-        <v>10.33</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="20">
@@ -31617,7 +31648,7 @@
         <v>103</v>
       </c>
       <c r="C20" t="n">
-        <v>10.33</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="21">
@@ -31628,7 +31659,7 @@
         <v>102</v>
       </c>
       <c r="C21" t="n">
-        <v>10.23</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="22">
@@ -31639,7 +31670,7 @@
         <v>102</v>
       </c>
       <c r="C22" t="n">
-        <v>10.23</v>
+        <v>10.22</v>
       </c>
     </row>
     <row r="23">
@@ -31650,7 +31681,7 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.13</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="24">
@@ -31661,7 +31692,7 @@
         <v>101</v>
       </c>
       <c r="C24" t="n">
-        <v>10.13</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="25">
@@ -31672,7 +31703,7 @@
         <v>101</v>
       </c>
       <c r="C25" t="n">
-        <v>10.13</v>
+        <v>10.12</v>
       </c>
     </row>
     <row r="26">
@@ -31683,7 +31714,7 @@
         <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="27">
@@ -31694,7 +31725,7 @@
         <v>100</v>
       </c>
       <c r="C27" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="28">
@@ -31705,7 +31736,7 @@
         <v>100</v>
       </c>
       <c r="C28" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="29">
@@ -31716,7 +31747,7 @@
         <v>99</v>
       </c>
       <c r="C29" t="n">
-        <v>9.93</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="30">
@@ -31727,7 +31758,7 @@
         <v>98</v>
       </c>
       <c r="C30" t="n">
-        <v>9.83</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="31">
@@ -31735,10 +31766,10 @@
         <v>22</v>
       </c>
       <c r="B31" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C31" t="n">
-        <v>9.73</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="32">
@@ -31749,7 +31780,7 @@
         <v>97</v>
       </c>
       <c r="C32" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -31760,7 +31791,7 @@
         <v>97</v>
       </c>
       <c r="C33" t="n">
-        <v>9.73</v>
+        <v>9.720000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -31771,7 +31802,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.630000000000001</v>
+        <v>9.619999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -31782,7 +31813,7 @@
         <v>95</v>
       </c>
       <c r="C35" t="n">
-        <v>9.529999999999999</v>
+        <v>9.52</v>
       </c>
     </row>
     <row r="36">
@@ -31793,7 +31824,7 @@
         <v>94</v>
       </c>
       <c r="C36" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="37">
@@ -31804,7 +31835,7 @@
         <v>94</v>
       </c>
       <c r="C37" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="38">
@@ -31815,7 +31846,7 @@
         <v>94</v>
       </c>
       <c r="C38" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="39">
@@ -31826,7 +31857,7 @@
         <v>94</v>
       </c>
       <c r="C39" t="n">
-        <v>9.43</v>
+        <v>9.42</v>
       </c>
     </row>
     <row r="40">
@@ -31837,7 +31868,7 @@
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.33</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="41">
@@ -31848,7 +31879,7 @@
         <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>9.33</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="42">
@@ -31859,7 +31890,7 @@
         <v>93</v>
       </c>
       <c r="C42" t="n">
-        <v>9.33</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="43">
@@ -31870,7 +31901,7 @@
         <v>90</v>
       </c>
       <c r="C43" t="n">
-        <v>9.029999999999999</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="44">
@@ -31881,7 +31912,7 @@
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.029999999999999</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="45">
@@ -31892,7 +31923,7 @@
         <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>9.029999999999999</v>
+        <v>9.02</v>
       </c>
     </row>
     <row r="46">
@@ -31903,7 +31934,7 @@
         <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.93</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="47">
@@ -31914,7 +31945,7 @@
         <v>89</v>
       </c>
       <c r="C47" t="n">
-        <v>8.93</v>
+        <v>8.92</v>
       </c>
     </row>
     <row r="48">
@@ -31925,7 +31956,7 @@
         <v>88</v>
       </c>
       <c r="C48" t="n">
-        <v>8.83</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="49">
@@ -31936,7 +31967,7 @@
         <v>88</v>
       </c>
       <c r="C49" t="n">
-        <v>8.83</v>
+        <v>8.82</v>
       </c>
     </row>
     <row r="50">
@@ -31947,7 +31978,7 @@
         <v>87</v>
       </c>
       <c r="C50" t="n">
-        <v>8.73</v>
+        <v>8.720000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -32000,7 +32031,7 @@
         <v>216</v>
       </c>
       <c r="C2" t="n">
-        <v>21.66</v>
+        <v>21.64</v>
       </c>
     </row>
     <row r="3">
@@ -32011,7 +32042,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.36</v>
+        <v>20.34</v>
       </c>
     </row>
     <row r="4">
@@ -32019,10 +32050,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C4" t="n">
-        <v>19.66</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="5">
@@ -32033,7 +32064,7 @@
         <v>194</v>
       </c>
       <c r="C5" t="n">
-        <v>19.46</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="6">
@@ -32041,10 +32072,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>18.96</v>
+        <v>19.04</v>
       </c>
     </row>
     <row r="7">
@@ -32055,7 +32086,7 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>18.46</v>
+        <v>18.44</v>
       </c>
     </row>
     <row r="8">
@@ -32066,7 +32097,7 @@
         <v>183</v>
       </c>
       <c r="C8" t="n">
-        <v>18.36</v>
+        <v>18.34</v>
       </c>
     </row>
     <row r="9">
@@ -32077,7 +32108,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.75</v>
+        <v>16.73</v>
       </c>
     </row>
     <row r="10">
@@ -32088,7 +32119,7 @@
         <v>163</v>
       </c>
       <c r="C10" t="n">
-        <v>16.35</v>
+        <v>16.33</v>
       </c>
     </row>
     <row r="11">
@@ -32099,7 +32130,7 @@
         <v>149</v>
       </c>
       <c r="C11" t="n">
-        <v>14.94</v>
+        <v>14.93</v>
       </c>
     </row>
     <row r="12">
@@ -32110,7 +32141,7 @@
         <v>85</v>
       </c>
       <c r="C12" t="n">
-        <v>8.529999999999999</v>
+        <v>8.52</v>
       </c>
     </row>
     <row r="13">
@@ -32121,7 +32152,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.52</v>
+        <v>6.51</v>
       </c>
     </row>
   </sheetData>
@@ -32163,7 +32194,7 @@
         <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>20.84</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="3">
@@ -32174,7 +32205,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.37</v>
+        <v>19.33</v>
       </c>
     </row>
     <row r="4">
@@ -32185,7 +32216,7 @@
         <v>85</v>
       </c>
       <c r="C4" t="n">
-        <v>17.89</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="5">
@@ -32196,7 +32227,7 @@
         <v>82</v>
       </c>
       <c r="C5" t="n">
-        <v>17.26</v>
+        <v>17.23</v>
       </c>
     </row>
     <row r="6">
@@ -32207,7 +32238,7 @@
         <v>82</v>
       </c>
       <c r="C6" t="n">
-        <v>17.26</v>
+        <v>17.23</v>
       </c>
     </row>
     <row r="7">
@@ -32218,7 +32249,7 @@
         <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>16.63</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="8">
@@ -32229,7 +32260,7 @@
         <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>16.42</v>
+        <v>16.39</v>
       </c>
     </row>
     <row r="9">
@@ -32237,10 +32268,10 @@
         <v>4</v>
       </c>
       <c r="B9" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>15.58</v>
+        <v>15.76</v>
       </c>
     </row>
     <row r="10">
@@ -32251,29 +32282,29 @@
         <v>74</v>
       </c>
       <c r="C10" t="n">
-        <v>15.58</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>14.74</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B12" t="n">
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.74</v>
+        <v>14.71</v>
       </c>
     </row>
     <row r="13">
@@ -32284,7 +32315,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.68</v>
+        <v>13.66</v>
       </c>
     </row>
   </sheetData>
@@ -32436,7 +32467,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>30 &amp; 43</t>
+          <t>11 &amp; 35</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -32446,7 +32477,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6 &amp; 21</t>
+          <t>30 &amp; 43</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -32456,7 +32487,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1 &amp; 18</t>
+          <t>6 &amp; 21</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -32466,7 +32497,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2 &amp; 30</t>
+          <t>1 &amp; 18</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -32476,7 +32507,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>36 &amp; 43</t>
+          <t>2 &amp; 30</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -32486,7 +32517,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>27 &amp; 41</t>
+          <t>36 &amp; 43</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -32496,7 +32527,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>35 &amp; 46</t>
+          <t>27 &amp; 41</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -32506,17 +32537,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>7 &amp; 19</t>
+          <t>35 &amp; 46</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>41 &amp; 45</t>
+          <t>7 &amp; 19</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -32526,7 +32557,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>39 &amp; 47</t>
+          <t>41 &amp; 45</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -32536,7 +32567,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>15 &amp; 18</t>
+          <t>39 &amp; 47</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -32546,7 +32577,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>9 &amp; 20</t>
+          <t>15 &amp; 18</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -32556,7 +32587,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>20 &amp; 49</t>
+          <t>9 &amp; 20</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -32780,13 +32811,13 @@
         <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2" t="n">
         <v>10.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.78</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="3">
@@ -32794,27 +32825,27 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
         <v>9.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>8.4</v>
+        <v>9.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.39</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="5">
@@ -32822,486 +32853,486 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
         <v>10.3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.89</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="B7" t="n">
         <v>18</v>
       </c>
       <c r="C7" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B8" t="n">
         <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>1.88</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="B9" t="n">
         <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10.3</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B10" t="n">
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>10.9</v>
       </c>
       <c r="D10" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D12" t="n">
-        <v>1.52</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>10.9</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="D14" t="n">
-        <v>1.49</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>9.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>1.27</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>37</v>
+      </c>
+      <c r="B16" t="n">
         <v>9</v>
       </c>
-      <c r="B16" t="n">
-        <v>11</v>
-      </c>
       <c r="C16" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>1.14</v>
+        <v>0.92</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B18" t="n">
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>8.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.03</v>
+        <v>0.99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B19" t="n">
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>9.5</v>
+        <v>11.1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.85</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="B20" t="n">
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>9.800000000000001</v>
+        <v>10.6</v>
       </c>
       <c r="D20" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B21" t="n">
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>8.699999999999999</v>
+        <v>11.2</v>
       </c>
       <c r="D21" t="n">
-        <v>0.92</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="B22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="D22" t="n">
-        <v>0.88</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="B23" t="n">
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
       <c r="D23" t="n">
-        <v>0.63</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="D24" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="D25" t="n">
-        <v>0.66</v>
+        <v>0.59</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>10.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.57</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>11.2</v>
+        <v>10.3</v>
       </c>
       <c r="D27" t="n">
-        <v>0.54</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="D28" t="n">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>9.199999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="D29" t="n">
-        <v>0.54</v>
+        <v>0.47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>10.2</v>
+        <v>12.3</v>
       </c>
       <c r="D30" t="n">
-        <v>0.49</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>10.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>0.39</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>10.7</v>
+        <v>8.9</v>
       </c>
       <c r="D32" t="n">
-        <v>0.37</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>10.3</v>
+        <v>11.5</v>
       </c>
       <c r="D33" t="n">
-        <v>0.39</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.24</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="B37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="D37" t="n">
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>9.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
       <c r="D39" t="n">
         <v>0.2</v>
@@ -33309,83 +33340,83 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="D41" t="n">
-        <v>0.23</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>10.2</v>
+        <v>9.4</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="D44" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="D45" t="n">
         <v>0.1</v>
@@ -33393,27 +33424,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>0.09</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33421,13 +33452,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33435,13 +33466,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>10.1</v>
+        <v>8.5</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33449,13 +33480,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33463,13 +33494,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I999"/>
+  <dimension ref="A1:I1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31409,6 +31409,37 @@
       </c>
       <c r="I999" t="n">
         <v>8</v>
+      </c>
+    </row>
+    <row r="1000">
+      <c r="A1000" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C1000" t="n">
+        <v>12</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>24</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>25</v>
+      </c>
+      <c r="F1000" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>45</v>
+      </c>
+      <c r="H1000" t="n">
+        <v>1</v>
+      </c>
+      <c r="I1000" t="n">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -31450,7 +31481,7 @@
         <v>116</v>
       </c>
       <c r="C2" t="n">
-        <v>11.62</v>
+        <v>11.61</v>
       </c>
     </row>
     <row r="3">
@@ -31461,7 +31492,7 @@
         <v>115</v>
       </c>
       <c r="C3" t="n">
-        <v>11.52</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="4">
@@ -31472,7 +31503,7 @@
         <v>115</v>
       </c>
       <c r="C4" t="n">
-        <v>11.52</v>
+        <v>11.51</v>
       </c>
     </row>
     <row r="5">
@@ -31483,7 +31514,7 @@
         <v>114</v>
       </c>
       <c r="C5" t="n">
-        <v>11.42</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="6">
@@ -31494,7 +31525,7 @@
         <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>11.22</v>
+        <v>11.21</v>
       </c>
     </row>
     <row r="7">
@@ -31505,7 +31536,7 @@
         <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
     </row>
     <row r="8">
@@ -31516,7 +31547,7 @@
         <v>109</v>
       </c>
       <c r="C8" t="n">
-        <v>10.92</v>
+        <v>10.91</v>
       </c>
     </row>
     <row r="9">
@@ -31527,7 +31558,7 @@
         <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>10.82</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="10">
@@ -31538,7 +31569,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>10.82</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="11">
@@ -31549,7 +31580,7 @@
         <v>108</v>
       </c>
       <c r="C11" t="n">
-        <v>10.82</v>
+        <v>10.81</v>
       </c>
     </row>
     <row r="12">
@@ -31560,7 +31591,7 @@
         <v>107</v>
       </c>
       <c r="C12" t="n">
-        <v>10.72</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="13">
@@ -31571,7 +31602,7 @@
         <v>107</v>
       </c>
       <c r="C13" t="n">
-        <v>10.72</v>
+        <v>10.71</v>
       </c>
     </row>
     <row r="14">
@@ -31582,7 +31613,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.52</v>
+        <v>10.51</v>
       </c>
     </row>
     <row r="15">
@@ -31593,7 +31624,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.42</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="16">
@@ -31604,7 +31635,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.42</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="17">
@@ -31615,7 +31646,7 @@
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.42</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="18">
@@ -31626,7 +31657,7 @@
         <v>104</v>
       </c>
       <c r="C18" t="n">
-        <v>10.42</v>
+        <v>10.41</v>
       </c>
     </row>
     <row r="19">
@@ -31637,29 +31668,29 @@
         <v>103</v>
       </c>
       <c r="C19" t="n">
-        <v>10.32</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B20" t="n">
         <v>103</v>
       </c>
       <c r="C20" t="n">
-        <v>10.32</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B21" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C21" t="n">
-        <v>10.22</v>
+        <v>10.31</v>
       </c>
     </row>
     <row r="22">
@@ -31670,7 +31701,7 @@
         <v>102</v>
       </c>
       <c r="C22" t="n">
-        <v>10.22</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="23">
@@ -31681,7 +31712,7 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="24">
@@ -31692,7 +31723,7 @@
         <v>101</v>
       </c>
       <c r="C24" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="25">
@@ -31703,7 +31734,7 @@
         <v>101</v>
       </c>
       <c r="C25" t="n">
-        <v>10.12</v>
+        <v>10.11</v>
       </c>
     </row>
     <row r="26">
@@ -31714,7 +31745,7 @@
         <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="27">
@@ -31725,7 +31756,7 @@
         <v>100</v>
       </c>
       <c r="C27" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="28">
@@ -31736,29 +31767,29 @@
         <v>100</v>
       </c>
       <c r="C28" t="n">
-        <v>10.02</v>
+        <v>10.01</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B29" t="n">
         <v>99</v>
       </c>
       <c r="C29" t="n">
-        <v>9.92</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="B30" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C30" t="n">
-        <v>9.82</v>
+        <v>9.91</v>
       </c>
     </row>
     <row r="31">
@@ -31769,7 +31800,7 @@
         <v>98</v>
       </c>
       <c r="C31" t="n">
-        <v>9.82</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="32">
@@ -31777,10 +31808,10 @@
         <v>29</v>
       </c>
       <c r="B32" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C32" t="n">
-        <v>9.720000000000001</v>
+        <v>9.81</v>
       </c>
     </row>
     <row r="33">
@@ -31791,7 +31822,7 @@
         <v>97</v>
       </c>
       <c r="C33" t="n">
-        <v>9.720000000000001</v>
+        <v>9.710000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -31802,7 +31833,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.619999999999999</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -31813,7 +31844,7 @@
         <v>95</v>
       </c>
       <c r="C35" t="n">
-        <v>9.52</v>
+        <v>9.51</v>
       </c>
     </row>
     <row r="36">
@@ -31824,7 +31855,7 @@
         <v>94</v>
       </c>
       <c r="C36" t="n">
-        <v>9.42</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="37">
@@ -31835,7 +31866,7 @@
         <v>94</v>
       </c>
       <c r="C37" t="n">
-        <v>9.42</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="38">
@@ -31846,7 +31877,7 @@
         <v>94</v>
       </c>
       <c r="C38" t="n">
-        <v>9.42</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="39">
@@ -31857,7 +31888,7 @@
         <v>94</v>
       </c>
       <c r="C39" t="n">
-        <v>9.42</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="40">
@@ -31868,7 +31899,7 @@
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.32</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="41">
@@ -31879,7 +31910,7 @@
         <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>9.32</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="42">
@@ -31890,29 +31921,29 @@
         <v>93</v>
       </c>
       <c r="C42" t="n">
-        <v>9.32</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B43" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C43" t="n">
-        <v>9.02</v>
+        <v>9.109999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B44" t="n">
         <v>90</v>
       </c>
       <c r="C44" t="n">
-        <v>9.02</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="45">
@@ -31923,51 +31954,51 @@
         <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>9.02</v>
+        <v>9.01</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B46" t="n">
         <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.92</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="B47" t="n">
         <v>89</v>
       </c>
       <c r="C47" t="n">
-        <v>8.92</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C48" t="n">
-        <v>8.82</v>
+        <v>8.91</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B49" t="n">
         <v>88</v>
       </c>
       <c r="C49" t="n">
-        <v>8.82</v>
+        <v>8.81</v>
       </c>
     </row>
     <row r="50">
@@ -31978,7 +32009,7 @@
         <v>87</v>
       </c>
       <c r="C50" t="n">
-        <v>8.720000000000001</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -31989,7 +32020,7 @@
         <v>80</v>
       </c>
       <c r="C51" t="n">
-        <v>8.02</v>
+        <v>8.01</v>
       </c>
     </row>
   </sheetData>
@@ -32031,7 +32062,7 @@
         <v>216</v>
       </c>
       <c r="C2" t="n">
-        <v>21.64</v>
+        <v>21.62</v>
       </c>
     </row>
     <row r="3">
@@ -32042,7 +32073,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.34</v>
+        <v>20.32</v>
       </c>
     </row>
     <row r="4">
@@ -32053,7 +32084,7 @@
         <v>197</v>
       </c>
       <c r="C4" t="n">
-        <v>19.74</v>
+        <v>19.72</v>
       </c>
     </row>
     <row r="5">
@@ -32064,7 +32095,7 @@
         <v>194</v>
       </c>
       <c r="C5" t="n">
-        <v>19.44</v>
+        <v>19.42</v>
       </c>
     </row>
     <row r="6">
@@ -32075,29 +32106,29 @@
         <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>19.04</v>
+        <v>19.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B7" t="n">
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>18.44</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C8" t="n">
-        <v>18.34</v>
+        <v>18.42</v>
       </c>
     </row>
     <row r="9">
@@ -32108,7 +32139,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.73</v>
+        <v>16.72</v>
       </c>
     </row>
     <row r="10">
@@ -32116,10 +32147,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C10" t="n">
-        <v>16.33</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="11">
@@ -32130,7 +32161,7 @@
         <v>149</v>
       </c>
       <c r="C11" t="n">
-        <v>14.93</v>
+        <v>14.91</v>
       </c>
     </row>
     <row r="12">
@@ -32141,7 +32172,7 @@
         <v>85</v>
       </c>
       <c r="C12" t="n">
-        <v>8.52</v>
+        <v>8.51</v>
       </c>
     </row>
     <row r="13">
@@ -32194,7 +32225,7 @@
         <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>20.8</v>
+        <v>20.75</v>
       </c>
     </row>
     <row r="3">
@@ -32205,7 +32236,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.33</v>
+        <v>19.29</v>
       </c>
     </row>
     <row r="4">
@@ -32216,7 +32247,7 @@
         <v>85</v>
       </c>
       <c r="C4" t="n">
-        <v>17.86</v>
+        <v>17.82</v>
       </c>
     </row>
     <row r="5">
@@ -32224,10 +32255,10 @@
         <v>1</v>
       </c>
       <c r="B5" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C5" t="n">
-        <v>17.23</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="6">
@@ -32238,7 +32269,7 @@
         <v>82</v>
       </c>
       <c r="C6" t="n">
-        <v>17.23</v>
+        <v>17.19</v>
       </c>
     </row>
     <row r="7">
@@ -32249,7 +32280,7 @@
         <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>16.6</v>
+        <v>16.56</v>
       </c>
     </row>
     <row r="8">
@@ -32260,7 +32291,7 @@
         <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>16.39</v>
+        <v>16.35</v>
       </c>
     </row>
     <row r="9">
@@ -32271,7 +32302,7 @@
         <v>75</v>
       </c>
       <c r="C9" t="n">
-        <v>15.76</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="10">
@@ -32279,10 +32310,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C10" t="n">
-        <v>15.55</v>
+        <v>15.72</v>
       </c>
     </row>
     <row r="11">
@@ -32293,7 +32324,7 @@
         <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>14.92</v>
+        <v>14.88</v>
       </c>
     </row>
     <row r="12">
@@ -32304,7 +32335,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.71</v>
+        <v>14.68</v>
       </c>
     </row>
     <row r="13">
@@ -32315,7 +32346,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.66</v>
+        <v>13.63</v>
       </c>
     </row>
   </sheetData>
@@ -32811,13 +32842,13 @@
         <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" t="n">
         <v>10.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.88</v>
+        <v>2.97</v>
       </c>
     </row>
     <row r="3">
@@ -32825,13 +32856,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
         <v>9.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.43</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="4">
@@ -32839,13 +32870,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>9.5</v>
       </c>
       <c r="D4" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="5">
@@ -32853,13 +32884,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
         <v>10.3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
     </row>
     <row r="6">
@@ -32867,13 +32898,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
         <v>9.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="7">
@@ -32881,13 +32912,13 @@
         <v>16</v>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>1.99</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="8">
@@ -32895,13 +32926,13 @@
         <v>26</v>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="9">
@@ -32909,111 +32940,111 @@
         <v>40</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>10.3</v>
       </c>
       <c r="D9" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
-        <v>10.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B13" t="n">
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B14" t="n">
         <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>10.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>1.05</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B15" t="n">
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>1.15</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.92</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="17">
@@ -33021,248 +33052,248 @@
         <v>14</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
         <v>9.5</v>
       </c>
       <c r="D17" t="n">
-        <v>0.95</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>49</v>
+        <v>5</v>
       </c>
       <c r="B18" t="n">
         <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>9.1</v>
+        <v>11.1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.99</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>5</v>
+        <v>42</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
       <c r="D19" t="n">
-        <v>0.72</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>10.6</v>
+        <v>11.2</v>
       </c>
       <c r="D20" t="n">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B21" t="n">
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="D21" t="n">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="B22" t="n">
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>11.2</v>
+        <v>10.4</v>
       </c>
       <c r="D22" t="n">
-        <v>0.63</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B23" t="n">
         <v>7</v>
       </c>
       <c r="C23" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="D23" t="n">
-        <v>0.66</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>10.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>0.58</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D25" t="n">
-        <v>0.59</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>9.199999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="D26" t="n">
-        <v>0.65</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B27" t="n">
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>10.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="D28" t="n">
-        <v>0.49</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>10</v>
+        <v>36</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>10.7</v>
+        <v>11.5</v>
       </c>
       <c r="D29" t="n">
-        <v>0.47</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>12.3</v>
+        <v>8.9</v>
       </c>
       <c r="D30" t="n">
-        <v>0.32</v>
+        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>0.45</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="B33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>11.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="D34" t="n">
         <v>0.3</v>
@@ -33270,111 +33301,111 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="D35" t="n">
-        <v>0.31</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>9.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="D36" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B37" t="n">
         <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>11.3</v>
+        <v>10.1</v>
       </c>
       <c r="D38" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>10.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="D40" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="D42" t="n">
         <v>0.11</v>
@@ -33382,35 +33413,35 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="D43" t="n">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
@@ -33424,27 +33455,27 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9.800000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33452,13 +33483,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>8.6</v>
+        <v>10.2</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33466,13 +33497,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>8.5</v>
+        <v>11.1</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33480,13 +33511,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>10.1</v>
+        <v>10.9</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33494,13 +33525,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>8.699999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1000"/>
+  <dimension ref="A1:I1001"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31439,6 +31439,37 @@
         <v>1</v>
       </c>
       <c r="I1000" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1001">
+      <c r="A1001" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C1001" t="n">
+        <v>5</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>16</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>32</v>
+      </c>
+      <c r="F1001" t="n">
+        <v>34</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>38</v>
+      </c>
+      <c r="H1001" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1001" t="n">
         <v>9</v>
       </c>
     </row>
@@ -31481,7 +31512,7 @@
         <v>116</v>
       </c>
       <c r="C2" t="n">
-        <v>11.61</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="3">
@@ -31492,29 +31523,29 @@
         <v>115</v>
       </c>
       <c r="C3" t="n">
-        <v>11.51</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B4" t="n">
         <v>115</v>
       </c>
       <c r="C4" t="n">
-        <v>11.51</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C5" t="n">
-        <v>11.41</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="6">
@@ -31525,7 +31556,7 @@
         <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>11.21</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="7">
@@ -31536,7 +31567,7 @@
         <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>11.11</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="8">
@@ -31544,10 +31575,10 @@
         <v>16</v>
       </c>
       <c r="B8" t="n">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>10.91</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9">
@@ -31558,7 +31589,7 @@
         <v>108</v>
       </c>
       <c r="C9" t="n">
-        <v>10.81</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="10">
@@ -31569,7 +31600,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>10.81</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="11">
@@ -31580,7 +31611,7 @@
         <v>108</v>
       </c>
       <c r="C11" t="n">
-        <v>10.81</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="12">
@@ -31591,7 +31622,7 @@
         <v>107</v>
       </c>
       <c r="C12" t="n">
-        <v>10.71</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="13">
@@ -31602,7 +31633,7 @@
         <v>107</v>
       </c>
       <c r="C13" t="n">
-        <v>10.71</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="14">
@@ -31613,7 +31644,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.51</v>
+        <v>10.5</v>
       </c>
     </row>
     <row r="15">
@@ -31624,7 +31655,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.41</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="16">
@@ -31635,7 +31666,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.41</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="17">
@@ -31646,7 +31677,7 @@
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.41</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="18">
@@ -31657,7 +31688,7 @@
         <v>104</v>
       </c>
       <c r="C18" t="n">
-        <v>10.41</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="19">
@@ -31668,7 +31699,7 @@
         <v>103</v>
       </c>
       <c r="C19" t="n">
-        <v>10.31</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="20">
@@ -31679,7 +31710,7 @@
         <v>103</v>
       </c>
       <c r="C20" t="n">
-        <v>10.31</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="21">
@@ -31690,7 +31721,7 @@
         <v>103</v>
       </c>
       <c r="C21" t="n">
-        <v>10.31</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="22">
@@ -31701,7 +31732,7 @@
         <v>102</v>
       </c>
       <c r="C22" t="n">
-        <v>10.21</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="23">
@@ -31712,7 +31743,7 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="24">
@@ -31723,7 +31754,7 @@
         <v>101</v>
       </c>
       <c r="C24" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="25">
@@ -31734,18 +31765,18 @@
         <v>101</v>
       </c>
       <c r="C25" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B26" t="n">
         <v>100</v>
       </c>
       <c r="C26" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
@@ -31756,40 +31787,40 @@
         <v>100</v>
       </c>
       <c r="C27" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B28" t="n">
         <v>100</v>
       </c>
       <c r="C28" t="n">
-        <v>10.01</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B29" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C29" t="n">
-        <v>9.91</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="B30" t="n">
         <v>99</v>
       </c>
       <c r="C30" t="n">
-        <v>9.91</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="31">
@@ -31800,7 +31831,7 @@
         <v>98</v>
       </c>
       <c r="C31" t="n">
-        <v>9.81</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -31811,7 +31842,7 @@
         <v>98</v>
       </c>
       <c r="C32" t="n">
-        <v>9.81</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -31822,7 +31853,7 @@
         <v>97</v>
       </c>
       <c r="C33" t="n">
-        <v>9.710000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -31833,7 +31864,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.609999999999999</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="35">
@@ -31844,7 +31875,7 @@
         <v>95</v>
       </c>
       <c r="C35" t="n">
-        <v>9.51</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="36">
@@ -31852,10 +31883,10 @@
         <v>32</v>
       </c>
       <c r="B36" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C36" t="n">
-        <v>9.41</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="37">
@@ -31866,7 +31897,7 @@
         <v>94</v>
       </c>
       <c r="C37" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="38">
@@ -31877,7 +31908,7 @@
         <v>94</v>
       </c>
       <c r="C38" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="39">
@@ -31888,7 +31919,7 @@
         <v>94</v>
       </c>
       <c r="C39" t="n">
-        <v>9.41</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="40">
@@ -31899,7 +31930,7 @@
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -31910,7 +31941,7 @@
         <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="42">
@@ -31921,29 +31952,29 @@
         <v>93</v>
       </c>
       <c r="C42" t="n">
-        <v>9.31</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B43" t="n">
         <v>91</v>
       </c>
       <c r="C43" t="n">
-        <v>9.109999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="B44" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>9.01</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="45">
@@ -31954,7 +31985,7 @@
         <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>9.01</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46">
@@ -31965,7 +31996,7 @@
         <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="47">
@@ -31976,7 +32007,7 @@
         <v>89</v>
       </c>
       <c r="C47" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="48">
@@ -31987,7 +32018,7 @@
         <v>89</v>
       </c>
       <c r="C48" t="n">
-        <v>8.91</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="49">
@@ -31998,7 +32029,7 @@
         <v>88</v>
       </c>
       <c r="C49" t="n">
-        <v>8.81</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -32009,7 +32040,7 @@
         <v>87</v>
       </c>
       <c r="C50" t="n">
-        <v>8.710000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -32020,7 +32051,7 @@
         <v>80</v>
       </c>
       <c r="C51" t="n">
-        <v>8.01</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -32062,7 +32093,7 @@
         <v>216</v>
       </c>
       <c r="C2" t="n">
-        <v>21.62</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="3">
@@ -32073,7 +32104,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.32</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="4">
@@ -32081,10 +32112,10 @@
         <v>8</v>
       </c>
       <c r="B4" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C4" t="n">
-        <v>19.72</v>
+        <v>19.8</v>
       </c>
     </row>
     <row r="5">
@@ -32095,7 +32126,7 @@
         <v>194</v>
       </c>
       <c r="C5" t="n">
-        <v>19.42</v>
+        <v>19.4</v>
       </c>
     </row>
     <row r="6">
@@ -32106,7 +32137,7 @@
         <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>19.02</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
@@ -32117,7 +32148,7 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>18.42</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="8">
@@ -32128,7 +32159,7 @@
         <v>184</v>
       </c>
       <c r="C8" t="n">
-        <v>18.42</v>
+        <v>18.4</v>
       </c>
     </row>
     <row r="9">
@@ -32139,7 +32170,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.72</v>
+        <v>16.7</v>
       </c>
     </row>
     <row r="10">
@@ -32147,10 +32178,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C10" t="n">
-        <v>16.42</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="11">
@@ -32161,7 +32192,7 @@
         <v>149</v>
       </c>
       <c r="C11" t="n">
-        <v>14.91</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="12">
@@ -32172,7 +32203,7 @@
         <v>85</v>
       </c>
       <c r="C12" t="n">
-        <v>8.51</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="13">
@@ -32183,7 +32214,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.51</v>
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -32225,7 +32256,7 @@
         <v>99</v>
       </c>
       <c r="C2" t="n">
-        <v>20.75</v>
+        <v>20.71</v>
       </c>
     </row>
     <row r="3">
@@ -32236,7 +32267,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.29</v>
+        <v>19.25</v>
       </c>
     </row>
     <row r="4">
@@ -32247,7 +32278,7 @@
         <v>85</v>
       </c>
       <c r="C4" t="n">
-        <v>17.82</v>
+        <v>17.78</v>
       </c>
     </row>
     <row r="5">
@@ -32258,7 +32289,7 @@
         <v>83</v>
       </c>
       <c r="C5" t="n">
-        <v>17.4</v>
+        <v>17.36</v>
       </c>
     </row>
     <row r="6">
@@ -32269,7 +32300,7 @@
         <v>82</v>
       </c>
       <c r="C6" t="n">
-        <v>17.19</v>
+        <v>17.15</v>
       </c>
     </row>
     <row r="7">
@@ -32280,7 +32311,7 @@
         <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>16.56</v>
+        <v>16.53</v>
       </c>
     </row>
     <row r="8">
@@ -32291,29 +32322,29 @@
         <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>16.35</v>
+        <v>16.32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>15.72</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B10" t="n">
         <v>75</v>
       </c>
       <c r="C10" t="n">
-        <v>15.72</v>
+        <v>15.69</v>
       </c>
     </row>
     <row r="11">
@@ -32321,10 +32352,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C11" t="n">
-        <v>14.88</v>
+        <v>15.06</v>
       </c>
     </row>
     <row r="12">
@@ -32335,7 +32366,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.68</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="13">
@@ -32346,7 +32377,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.63</v>
+        <v>13.6</v>
       </c>
     </row>
   </sheetData>
@@ -32428,7 +32459,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14 &amp; 34</t>
+          <t>16 &amp; 34</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -32438,7 +32469,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6 &amp; 49</t>
+          <t>14 &amp; 34</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -32448,7 +32479,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1 &amp; 7</t>
+          <t>6 &amp; 49</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -32458,7 +32489,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>11 &amp; 23</t>
+          <t>1 &amp; 7</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -32468,7 +32499,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21 &amp; 34</t>
+          <t>11 &amp; 23</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -32478,11 +32509,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>16 &amp; 34</t>
+          <t>21 &amp; 34</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -32842,13 +32873,13 @@
         <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C2" t="n">
         <v>10.4</v>
       </c>
       <c r="D2" t="n">
-        <v>2.97</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="3">
@@ -32856,13 +32887,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
         <v>9.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.54</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="4">
@@ -32870,13 +32901,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
         <v>9.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="5">
@@ -32884,13 +32915,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>10.3</v>
       </c>
       <c r="D5" t="n">
-        <v>1.94</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="6">
@@ -32898,374 +32929,374 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>9.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="B7" t="n">
         <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="D8" t="n">
-        <v>1.64</v>
+        <v>1.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B9" t="n">
         <v>18</v>
       </c>
       <c r="C9" t="n">
-        <v>10.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
+        <v>39</v>
+      </c>
+      <c r="B10" t="n">
         <v>15</v>
       </c>
-      <c r="B10" t="n">
-        <v>17</v>
-      </c>
       <c r="C10" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D10" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>9.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="D12" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="D13" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B14" t="n">
         <v>11</v>
       </c>
       <c r="C14" t="n">
-        <v>8.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>1.26</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="B15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>9.800000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.02</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B16" t="n">
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="B17" t="n">
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>9.5</v>
+        <v>10.6</v>
       </c>
       <c r="D17" t="n">
-        <v>1.06</v>
+        <v>0.9399999999999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>11.1</v>
+        <v>10.2</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>10.6</v>
+        <v>10.4</v>
       </c>
       <c r="D19" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>11.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="D21" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="B22" t="n">
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>10.4</v>
+        <v>10.7</v>
       </c>
       <c r="D22" t="n">
-        <v>0.67</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>10.2</v>
+        <v>11.5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.68</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>9.199999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="D24" t="n">
-        <v>0.76</v>
+        <v>0.67</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>10.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>0.58</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>10</v>
+        <v>48</v>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>10.7</v>
+        <v>12.3</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B27" t="n">
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>0.54</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>0.41</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C29" t="n">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>8.9</v>
+        <v>11.3</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="D31" t="n">
-        <v>0.41</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D32" t="n">
         <v>0.41</v>
@@ -33273,77 +33304,77 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B33" t="n">
         <v>3</v>
       </c>
       <c r="C33" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="D35" t="n">
-        <v>0.27</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="D36" t="n">
-        <v>0.26</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B37" t="n">
         <v>2</v>
       </c>
       <c r="C37" t="n">
-        <v>9.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
@@ -33357,13 +33388,13 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="D39" t="n">
         <v>0.22</v>
@@ -33371,111 +33402,111 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>9.4</v>
+        <v>8.5</v>
       </c>
       <c r="D41" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="D42" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>8.6</v>
+        <v>10.9</v>
       </c>
       <c r="D43" t="n">
-        <v>0.12</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>8.699999999999999</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>8.5</v>
+        <v>10.2</v>
       </c>
       <c r="D46" t="n">
-        <v>0.12</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33483,13 +33514,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>10.2</v>
+        <v>9.1</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33497,13 +33528,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33511,13 +33542,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>10.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33525,13 +33556,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>9.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1001"/>
+  <dimension ref="A1:I1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31471,6 +31471,37 @@
       </c>
       <c r="I1001" t="n">
         <v>9</v>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C1002" t="n">
+        <v>15</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>20</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>23</v>
+      </c>
+      <c r="F1002" t="n">
+        <v>29</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>30</v>
+      </c>
+      <c r="H1002" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1002" t="n">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -31509,10 +31540,10 @@
         <v>20</v>
       </c>
       <c r="B2" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C2" t="n">
-        <v>11.6</v>
+        <v>11.69</v>
       </c>
     </row>
     <row r="3">
@@ -31523,7 +31554,7 @@
         <v>115</v>
       </c>
       <c r="C3" t="n">
-        <v>11.5</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="4">
@@ -31534,7 +31565,7 @@
         <v>115</v>
       </c>
       <c r="C4" t="n">
-        <v>11.5</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="5">
@@ -31545,7 +31576,7 @@
         <v>115</v>
       </c>
       <c r="C5" t="n">
-        <v>11.5</v>
+        <v>11.49</v>
       </c>
     </row>
     <row r="6">
@@ -31556,7 +31587,7 @@
         <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>11.2</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="7">
@@ -31567,7 +31598,7 @@
         <v>111</v>
       </c>
       <c r="C7" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
     </row>
     <row r="8">
@@ -31578,62 +31609,62 @@
         <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C9" t="n">
-        <v>10.8</v>
+        <v>10.89</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="B10" t="n">
         <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>10.8</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>49</v>
+        <v>18</v>
       </c>
       <c r="B11" t="n">
         <v>108</v>
       </c>
       <c r="C11" t="n">
-        <v>10.8</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="B12" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C12" t="n">
-        <v>10.7</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B13" t="n">
         <v>107</v>
       </c>
       <c r="C13" t="n">
-        <v>10.7</v>
+        <v>10.69</v>
       </c>
     </row>
     <row r="14">
@@ -31644,7 +31675,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.5</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="15">
@@ -31655,7 +31686,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.4</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="16">
@@ -31666,7 +31697,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.4</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="17">
@@ -31677,7 +31708,7 @@
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.4</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="18">
@@ -31688,7 +31719,7 @@
         <v>104</v>
       </c>
       <c r="C18" t="n">
-        <v>10.4</v>
+        <v>10.39</v>
       </c>
     </row>
     <row r="19">
@@ -31699,7 +31730,7 @@
         <v>103</v>
       </c>
       <c r="C19" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="20">
@@ -31710,7 +31741,7 @@
         <v>103</v>
       </c>
       <c r="C20" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="21">
@@ -31721,7 +31752,7 @@
         <v>103</v>
       </c>
       <c r="C21" t="n">
-        <v>10.3</v>
+        <v>10.29</v>
       </c>
     </row>
     <row r="22">
@@ -31732,7 +31763,7 @@
         <v>102</v>
       </c>
       <c r="C22" t="n">
-        <v>10.2</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="23">
@@ -31743,7 +31774,7 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="24">
@@ -31754,7 +31785,7 @@
         <v>101</v>
       </c>
       <c r="C24" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="25">
@@ -31765,29 +31796,29 @@
         <v>101</v>
       </c>
       <c r="C25" t="n">
-        <v>10.1</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="B26" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>15</v>
+        <v>38</v>
       </c>
       <c r="B27" t="n">
         <v>100</v>
       </c>
       <c r="C27" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="28">
@@ -31798,7 +31829,7 @@
         <v>100</v>
       </c>
       <c r="C28" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="29">
@@ -31809,7 +31840,7 @@
         <v>100</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="30">
@@ -31820,29 +31851,29 @@
         <v>99</v>
       </c>
       <c r="C30" t="n">
-        <v>9.9</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="B31" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C31" t="n">
-        <v>9.800000000000001</v>
+        <v>9.890000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="B32" t="n">
         <v>98</v>
       </c>
       <c r="C32" t="n">
-        <v>9.800000000000001</v>
+        <v>9.789999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -31853,7 +31884,7 @@
         <v>97</v>
       </c>
       <c r="C33" t="n">
-        <v>9.699999999999999</v>
+        <v>9.69</v>
       </c>
     </row>
     <row r="34">
@@ -31864,7 +31895,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.6</v>
+        <v>9.59</v>
       </c>
     </row>
     <row r="35">
@@ -31875,7 +31906,7 @@
         <v>95</v>
       </c>
       <c r="C35" t="n">
-        <v>9.5</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="36">
@@ -31886,7 +31917,7 @@
         <v>95</v>
       </c>
       <c r="C36" t="n">
-        <v>9.5</v>
+        <v>9.49</v>
       </c>
     </row>
     <row r="37">
@@ -31897,7 +31928,7 @@
         <v>94</v>
       </c>
       <c r="C37" t="n">
-        <v>9.4</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -31908,7 +31939,7 @@
         <v>94</v>
       </c>
       <c r="C38" t="n">
-        <v>9.4</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -31919,7 +31950,7 @@
         <v>94</v>
       </c>
       <c r="C39" t="n">
-        <v>9.4</v>
+        <v>9.390000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -31930,7 +31961,7 @@
         <v>93</v>
       </c>
       <c r="C40" t="n">
-        <v>9.300000000000001</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -31941,7 +31972,7 @@
         <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>9.300000000000001</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="42">
@@ -31952,7 +31983,7 @@
         <v>93</v>
       </c>
       <c r="C42" t="n">
-        <v>9.300000000000001</v>
+        <v>9.289999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -31963,7 +31994,7 @@
         <v>91</v>
       </c>
       <c r="C43" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="44">
@@ -31974,7 +32005,7 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>9.1</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="45">
@@ -31985,7 +32016,7 @@
         <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>9</v>
+        <v>8.99</v>
       </c>
     </row>
     <row r="46">
@@ -31996,7 +32027,7 @@
         <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -32007,7 +32038,7 @@
         <v>89</v>
       </c>
       <c r="C47" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -32018,7 +32049,7 @@
         <v>89</v>
       </c>
       <c r="C48" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -32029,7 +32060,7 @@
         <v>88</v>
       </c>
       <c r="C49" t="n">
-        <v>8.800000000000001</v>
+        <v>8.789999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -32040,7 +32071,7 @@
         <v>87</v>
       </c>
       <c r="C50" t="n">
-        <v>8.699999999999999</v>
+        <v>8.69</v>
       </c>
     </row>
     <row r="51">
@@ -32051,7 +32082,7 @@
         <v>80</v>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>7.99</v>
       </c>
     </row>
   </sheetData>
@@ -32090,10 +32121,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C2" t="n">
-        <v>21.6</v>
+        <v>21.68</v>
       </c>
     </row>
     <row r="3">
@@ -32104,7 +32135,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.3</v>
+        <v>20.28</v>
       </c>
     </row>
     <row r="4">
@@ -32115,7 +32146,7 @@
         <v>198</v>
       </c>
       <c r="C4" t="n">
-        <v>19.8</v>
+        <v>19.78</v>
       </c>
     </row>
     <row r="5">
@@ -32126,7 +32157,7 @@
         <v>194</v>
       </c>
       <c r="C5" t="n">
-        <v>19.4</v>
+        <v>19.38</v>
       </c>
     </row>
     <row r="6">
@@ -32137,7 +32168,7 @@
         <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>19</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="7">
@@ -32148,7 +32179,7 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>18.4</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="8">
@@ -32159,7 +32190,7 @@
         <v>184</v>
       </c>
       <c r="C8" t="n">
-        <v>18.4</v>
+        <v>18.38</v>
       </c>
     </row>
     <row r="9">
@@ -32170,7 +32201,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.7</v>
+        <v>16.68</v>
       </c>
     </row>
     <row r="10">
@@ -32181,7 +32212,7 @@
         <v>165</v>
       </c>
       <c r="C10" t="n">
-        <v>16.5</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="11">
@@ -32192,7 +32223,7 @@
         <v>149</v>
       </c>
       <c r="C11" t="n">
-        <v>14.9</v>
+        <v>14.89</v>
       </c>
     </row>
     <row r="12">
@@ -32200,10 +32231,10 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C12" t="n">
-        <v>8.5</v>
+        <v>8.59</v>
       </c>
     </row>
     <row r="13">
@@ -32214,7 +32245,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
     </row>
   </sheetData>
@@ -32253,10 +32284,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>20.71</v>
+        <v>20.88</v>
       </c>
     </row>
     <row r="3">
@@ -32267,7 +32298,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.25</v>
+        <v>19.21</v>
       </c>
     </row>
     <row r="4">
@@ -32275,10 +32306,10 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C4" t="n">
-        <v>17.78</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="5">
@@ -32289,7 +32320,7 @@
         <v>83</v>
       </c>
       <c r="C5" t="n">
-        <v>17.36</v>
+        <v>17.33</v>
       </c>
     </row>
     <row r="6">
@@ -32300,7 +32331,7 @@
         <v>82</v>
       </c>
       <c r="C6" t="n">
-        <v>17.15</v>
+        <v>17.12</v>
       </c>
     </row>
     <row r="7">
@@ -32311,7 +32342,7 @@
         <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>16.53</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="8">
@@ -32322,7 +32353,7 @@
         <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>16.32</v>
+        <v>16.28</v>
       </c>
     </row>
     <row r="9">
@@ -32333,7 +32364,7 @@
         <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>15.9</v>
+        <v>15.87</v>
       </c>
     </row>
     <row r="10">
@@ -32344,7 +32375,7 @@
         <v>75</v>
       </c>
       <c r="C10" t="n">
-        <v>15.69</v>
+        <v>15.66</v>
       </c>
     </row>
     <row r="11">
@@ -32355,7 +32386,7 @@
         <v>72</v>
       </c>
       <c r="C11" t="n">
-        <v>15.06</v>
+        <v>15.03</v>
       </c>
     </row>
     <row r="12">
@@ -32366,7 +32397,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.64</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="13">
@@ -32377,7 +32408,7 @@
         <v>65</v>
       </c>
       <c r="C13" t="n">
-        <v>13.6</v>
+        <v>13.57</v>
       </c>
     </row>
   </sheetData>
@@ -32599,7 +32630,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>35 &amp; 46</t>
+          <t>15 &amp; 29</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -32609,17 +32640,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>7 &amp; 19</t>
+          <t>35 &amp; 46</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>41 &amp; 45</t>
+          <t>7 &amp; 19</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -32629,7 +32660,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>39 &amp; 47</t>
+          <t>41 &amp; 45</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -32639,7 +32670,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>15 &amp; 18</t>
+          <t>39 &amp; 47</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -32649,7 +32680,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>9 &amp; 20</t>
+          <t>15 &amp; 18</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -32873,13 +32904,13 @@
         <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C2" t="n">
         <v>10.4</v>
       </c>
       <c r="D2" t="n">
-        <v>3.07</v>
+        <v>3.17</v>
       </c>
     </row>
     <row r="3">
@@ -32887,13 +32918,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
         <v>9.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="4">
@@ -32901,13 +32932,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>9.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="5">
@@ -32915,13 +32946,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
         <v>10.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.04</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="6">
@@ -32929,13 +32960,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
         <v>9.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.31</v>
+        <v>2.42</v>
       </c>
     </row>
     <row r="7">
@@ -32943,13 +32974,13 @@
         <v>26</v>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>1.73</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="8">
@@ -32957,209 +32988,209 @@
         <v>40</v>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
         <v>10.3</v>
       </c>
       <c r="D8" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>39</v>
+        <v>9</v>
       </c>
       <c r="B10" t="n">
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>9.5</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B11" t="n">
         <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>9.699999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" t="n">
-        <v>10.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>9.5</v>
+        <v>9.1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="B14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.12</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="B15" t="n">
         <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
       <c r="D15" t="n">
-        <v>1.21</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="B16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>11.2</v>
+        <v>10.6</v>
       </c>
       <c r="D16" t="n">
-        <v>0.89</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>10.6</v>
+        <v>10.2</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>10.2</v>
+        <v>10.4</v>
       </c>
       <c r="D18" t="n">
-        <v>0.78</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="B19" t="n">
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>10.4</v>
+        <v>10.3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="B20" t="n">
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>9.199999999999999</v>
+        <v>10.7</v>
       </c>
       <c r="D20" t="n">
-        <v>0.87</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B21" t="n">
         <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="D21" t="n">
-        <v>0.68</v>
+        <v>0.57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B22" t="n">
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>10.7</v>
+        <v>8.9</v>
       </c>
       <c r="D22" t="n">
-        <v>0.65</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="23">
@@ -33167,192 +33198,192 @@
         <v>36</v>
       </c>
       <c r="B23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C23" t="n">
         <v>11.5</v>
       </c>
       <c r="D23" t="n">
-        <v>0.52</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B24" t="n">
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.67</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="B26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C26" t="n">
-        <v>12.3</v>
+        <v>10</v>
       </c>
       <c r="D26" t="n">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B27" t="n">
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>6</v>
+        <v>50</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="D28" t="n">
-        <v>0.51</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>11.3</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B30" t="n">
         <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>11.3</v>
+        <v>9.4</v>
       </c>
       <c r="D30" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>11</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>0.36</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.41</v>
+        <v>0.43</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>18</v>
+        <v>43</v>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="D33" t="n">
-        <v>0.32</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="D35" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="D36" t="n">
         <v>0.3</v>
@@ -33363,122 +33394,122 @@
         <v>35</v>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C37" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>0.23</v>
+        <v>0.35</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="D39" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>17</v>
+        <v>45</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>8.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>8.5</v>
+        <v>10.9</v>
       </c>
       <c r="D41" t="n">
-        <v>0.24</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>10.9</v>
+        <v>9.1</v>
       </c>
       <c r="D43" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>9.699999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>11.1</v>
+        <v>10.6</v>
       </c>
       <c r="D45" t="n">
         <v>0.09</v>
@@ -33486,13 +33517,13 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>10.2</v>
+        <v>10.1</v>
       </c>
       <c r="D46" t="n">
         <v>0.1</v>
@@ -33500,13 +33531,13 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>11.1</v>
+        <v>9.9</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33514,13 +33545,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>9.1</v>
+        <v>10.1</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33528,13 +33559,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>10.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33542,13 +33573,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33556,13 +33587,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1002"/>
+  <dimension ref="A1:I1003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31501,6 +31501,37 @@
         <v>5</v>
       </c>
       <c r="I1002" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1003">
+      <c r="A1003" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>Tuesday</t>
+        </is>
+      </c>
+      <c r="C1003" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>33</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>38</v>
+      </c>
+      <c r="F1003" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>47</v>
+      </c>
+      <c r="H1003" t="n">
+        <v>11</v>
+      </c>
+      <c r="I1003" t="n">
         <v>12</v>
       </c>
     </row>
@@ -31543,7 +31574,7 @@
         <v>117</v>
       </c>
       <c r="C2" t="n">
-        <v>11.69</v>
+        <v>11.68</v>
       </c>
     </row>
     <row r="3">
@@ -31554,7 +31585,7 @@
         <v>115</v>
       </c>
       <c r="C3" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="4">
@@ -31565,7 +31596,7 @@
         <v>115</v>
       </c>
       <c r="C4" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="5">
@@ -31576,7 +31607,7 @@
         <v>115</v>
       </c>
       <c r="C5" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
     </row>
     <row r="6">
@@ -31587,7 +31618,7 @@
         <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>11.19</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="7">
@@ -31595,10 +31626,10 @@
         <v>11</v>
       </c>
       <c r="B7" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>11.09</v>
+        <v>11.18</v>
       </c>
     </row>
     <row r="8">
@@ -31609,7 +31640,7 @@
         <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>10.99</v>
+        <v>10.98</v>
       </c>
     </row>
     <row r="9">
@@ -31620,7 +31651,7 @@
         <v>109</v>
       </c>
       <c r="C9" t="n">
-        <v>10.89</v>
+        <v>10.88</v>
       </c>
     </row>
     <row r="10">
@@ -31631,7 +31662,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>10.79</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="11">
@@ -31642,7 +31673,7 @@
         <v>108</v>
       </c>
       <c r="C11" t="n">
-        <v>10.79</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="12">
@@ -31653,7 +31684,7 @@
         <v>108</v>
       </c>
       <c r="C12" t="n">
-        <v>10.79</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="13">
@@ -31664,7 +31695,7 @@
         <v>107</v>
       </c>
       <c r="C13" t="n">
-        <v>10.69</v>
+        <v>10.68</v>
       </c>
     </row>
     <row r="14">
@@ -31675,7 +31706,7 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.49</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="15">
@@ -31686,7 +31717,7 @@
         <v>104</v>
       </c>
       <c r="C15" t="n">
-        <v>10.39</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="16">
@@ -31697,7 +31728,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.39</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="17">
@@ -31708,7 +31739,7 @@
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.39</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="18">
@@ -31719,7 +31750,7 @@
         <v>104</v>
       </c>
       <c r="C18" t="n">
-        <v>10.39</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="19">
@@ -31730,7 +31761,7 @@
         <v>103</v>
       </c>
       <c r="C19" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="20">
@@ -31741,7 +31772,7 @@
         <v>103</v>
       </c>
       <c r="C20" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="21">
@@ -31752,7 +31783,7 @@
         <v>103</v>
       </c>
       <c r="C21" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
     </row>
     <row r="22">
@@ -31763,7 +31794,7 @@
         <v>102</v>
       </c>
       <c r="C22" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="23">
@@ -31774,18 +31805,18 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B24" t="n">
         <v>101</v>
       </c>
       <c r="C24" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="25">
@@ -31796,29 +31827,29 @@
         <v>101</v>
       </c>
       <c r="C25" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B26" t="n">
         <v>101</v>
       </c>
       <c r="C26" t="n">
-        <v>10.09</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="B27" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C27" t="n">
-        <v>9.99</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="28">
@@ -31829,7 +31860,7 @@
         <v>100</v>
       </c>
       <c r="C28" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="29">
@@ -31840,7 +31871,7 @@
         <v>100</v>
       </c>
       <c r="C29" t="n">
-        <v>9.99</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="30">
@@ -31851,7 +31882,7 @@
         <v>99</v>
       </c>
       <c r="C30" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -31862,7 +31893,7 @@
         <v>99</v>
       </c>
       <c r="C31" t="n">
-        <v>9.890000000000001</v>
+        <v>9.880000000000001</v>
       </c>
     </row>
     <row r="32">
@@ -31873,7 +31904,7 @@
         <v>98</v>
       </c>
       <c r="C32" t="n">
-        <v>9.789999999999999</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -31881,10 +31912,10 @@
         <v>47</v>
       </c>
       <c r="B33" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C33" t="n">
-        <v>9.69</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -31895,7 +31926,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.59</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="35">
@@ -31903,10 +31934,10 @@
         <v>33</v>
       </c>
       <c r="B35" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C35" t="n">
-        <v>9.49</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="36">
@@ -31917,7 +31948,7 @@
         <v>95</v>
       </c>
       <c r="C36" t="n">
-        <v>9.49</v>
+        <v>9.48</v>
       </c>
     </row>
     <row r="37">
@@ -31928,7 +31959,7 @@
         <v>94</v>
       </c>
       <c r="C37" t="n">
-        <v>9.390000000000001</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -31939,7 +31970,7 @@
         <v>94</v>
       </c>
       <c r="C38" t="n">
-        <v>9.390000000000001</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -31950,18 +31981,18 @@
         <v>94</v>
       </c>
       <c r="C39" t="n">
-        <v>9.390000000000001</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" t="n">
-        <v>9.289999999999999</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="41">
@@ -31972,18 +32003,18 @@
         <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>9.289999999999999</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n">
         <v>93</v>
       </c>
       <c r="C42" t="n">
-        <v>9.289999999999999</v>
+        <v>9.279999999999999</v>
       </c>
     </row>
     <row r="43">
@@ -31994,7 +32025,7 @@
         <v>91</v>
       </c>
       <c r="C43" t="n">
-        <v>9.09</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="44">
@@ -32005,7 +32036,7 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>9.09</v>
+        <v>9.08</v>
       </c>
     </row>
     <row r="45">
@@ -32016,7 +32047,7 @@
         <v>90</v>
       </c>
       <c r="C45" t="n">
-        <v>8.99</v>
+        <v>8.98</v>
       </c>
     </row>
     <row r="46">
@@ -32027,7 +32058,7 @@
         <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.890000000000001</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -32038,7 +32069,7 @@
         <v>89</v>
       </c>
       <c r="C47" t="n">
-        <v>8.890000000000001</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -32049,7 +32080,7 @@
         <v>89</v>
       </c>
       <c r="C48" t="n">
-        <v>8.890000000000001</v>
+        <v>8.880000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -32060,7 +32091,7 @@
         <v>88</v>
       </c>
       <c r="C49" t="n">
-        <v>8.789999999999999</v>
+        <v>8.779999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -32071,7 +32102,7 @@
         <v>87</v>
       </c>
       <c r="C50" t="n">
-        <v>8.69</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="51">
@@ -32082,7 +32113,7 @@
         <v>80</v>
       </c>
       <c r="C51" t="n">
-        <v>7.99</v>
+        <v>7.98</v>
       </c>
     </row>
   </sheetData>
@@ -32124,7 +32155,7 @@
         <v>217</v>
       </c>
       <c r="C2" t="n">
-        <v>21.68</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="3">
@@ -32135,7 +32166,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.28</v>
+        <v>20.26</v>
       </c>
     </row>
     <row r="4">
@@ -32146,7 +32177,7 @@
         <v>198</v>
       </c>
       <c r="C4" t="n">
-        <v>19.78</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="5">
@@ -32157,7 +32188,7 @@
         <v>194</v>
       </c>
       <c r="C5" t="n">
-        <v>19.38</v>
+        <v>19.36</v>
       </c>
     </row>
     <row r="6">
@@ -32168,7 +32199,7 @@
         <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>18.98</v>
+        <v>18.96</v>
       </c>
     </row>
     <row r="7">
@@ -32179,7 +32210,7 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>18.38</v>
+        <v>18.36</v>
       </c>
     </row>
     <row r="8">
@@ -32190,7 +32221,7 @@
         <v>184</v>
       </c>
       <c r="C8" t="n">
-        <v>18.38</v>
+        <v>18.36</v>
       </c>
     </row>
     <row r="9">
@@ -32201,7 +32232,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.68</v>
+        <v>16.67</v>
       </c>
     </row>
     <row r="10">
@@ -32212,7 +32243,7 @@
         <v>165</v>
       </c>
       <c r="C10" t="n">
-        <v>16.48</v>
+        <v>16.47</v>
       </c>
     </row>
     <row r="11">
@@ -32223,7 +32254,7 @@
         <v>149</v>
       </c>
       <c r="C11" t="n">
-        <v>14.89</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="12">
@@ -32231,10 +32262,10 @@
         <v>12</v>
       </c>
       <c r="B12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C12" t="n">
-        <v>8.59</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="13">
@@ -32242,10 +32273,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13" t="n">
-        <v>6.49</v>
+        <v>6.59</v>
       </c>
     </row>
   </sheetData>
@@ -32287,7 +32318,7 @@
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>20.88</v>
+        <v>20.83</v>
       </c>
     </row>
     <row r="3">
@@ -32298,7 +32329,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.21</v>
+        <v>19.17</v>
       </c>
     </row>
     <row r="4">
@@ -32306,10 +32337,10 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C4" t="n">
-        <v>17.95</v>
+        <v>18.12</v>
       </c>
     </row>
     <row r="5">
@@ -32320,7 +32351,7 @@
         <v>83</v>
       </c>
       <c r="C5" t="n">
-        <v>17.33</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="6">
@@ -32331,7 +32362,7 @@
         <v>82</v>
       </c>
       <c r="C6" t="n">
-        <v>17.12</v>
+        <v>17.08</v>
       </c>
     </row>
     <row r="7">
@@ -32342,7 +32373,7 @@
         <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>16.49</v>
+        <v>16.46</v>
       </c>
     </row>
     <row r="8">
@@ -32353,7 +32384,7 @@
         <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>16.28</v>
+        <v>16.25</v>
       </c>
     </row>
     <row r="9">
@@ -32364,7 +32395,7 @@
         <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>15.87</v>
+        <v>15.83</v>
       </c>
     </row>
     <row r="10">
@@ -32375,7 +32406,7 @@
         <v>75</v>
       </c>
       <c r="C10" t="n">
-        <v>15.66</v>
+        <v>15.62</v>
       </c>
     </row>
     <row r="11">
@@ -32386,7 +32417,7 @@
         <v>72</v>
       </c>
       <c r="C11" t="n">
-        <v>15.03</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -32397,7 +32428,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.61</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="13">
@@ -32405,10 +32436,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C13" t="n">
-        <v>13.57</v>
+        <v>13.75</v>
       </c>
     </row>
   </sheetData>
@@ -32620,7 +32651,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>27 &amp; 41</t>
+          <t>11 &amp; 42</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -32630,7 +32661,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15 &amp; 29</t>
+          <t>27 &amp; 41</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -32640,7 +32671,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>35 &amp; 46</t>
+          <t>15 &amp; 29</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -32650,17 +32681,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>7 &amp; 19</t>
+          <t>35 &amp; 46</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>41 &amp; 45</t>
+          <t>7 &amp; 19</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -32670,7 +32701,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>39 &amp; 47</t>
+          <t>41 &amp; 45</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -32680,7 +32711,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>15 &amp; 18</t>
+          <t>39 &amp; 47</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -32904,13 +32935,13 @@
         <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
         <v>10.4</v>
       </c>
       <c r="D2" t="n">
-        <v>3.17</v>
+        <v>3.26</v>
       </c>
     </row>
     <row r="3">
@@ -32918,13 +32949,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="n">
         <v>9.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="4">
@@ -32932,13 +32963,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
         <v>9.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.31</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="5">
@@ -32946,13 +32977,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
         <v>10.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="6">
@@ -32960,13 +32991,13 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
         <v>9.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.42</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="7">
@@ -32974,13 +33005,13 @@
         <v>26</v>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="8">
@@ -32988,13 +33019,13 @@
         <v>40</v>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>10.3</v>
       </c>
       <c r="D8" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="9">
@@ -33002,13 +33033,13 @@
         <v>39</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>9.5</v>
       </c>
       <c r="D9" t="n">
-        <v>1.69</v>
+        <v>1.79</v>
       </c>
     </row>
     <row r="10">
@@ -33016,13 +33047,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>1.55</v>
+        <v>1.65</v>
       </c>
     </row>
     <row r="11">
@@ -33030,13 +33061,13 @@
         <v>31</v>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
         <v>10.4</v>
       </c>
       <c r="D11" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="12">
@@ -33044,13 +33075,13 @@
         <v>37</v>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="13">
@@ -33058,13 +33089,13 @@
         <v>49</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
         <v>9.1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.32</v>
+        <v>1.43</v>
       </c>
     </row>
     <row r="14">
@@ -33072,13 +33103,13 @@
         <v>14</v>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
         <v>9.5</v>
       </c>
       <c r="D14" t="n">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="15">
@@ -33086,458 +33117,458 @@
         <v>27</v>
       </c>
       <c r="B15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>11.2</v>
       </c>
       <c r="D15" t="n">
-        <v>0.98</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>42</v>
+        <v>2</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="D16" t="n">
-        <v>1.04</v>
+        <v>0.88</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>47</v>
+        <v>10</v>
       </c>
       <c r="B17" t="n">
         <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>10.2</v>
+        <v>10.7</v>
       </c>
       <c r="D17" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>10.4</v>
+        <v>11.5</v>
       </c>
       <c r="D18" t="n">
-        <v>0.87</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B19" t="n">
         <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="D19" t="n">
-        <v>0.78</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B20" t="n">
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>10.7</v>
+        <v>8.9</v>
       </c>
       <c r="D20" t="n">
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="B21" t="n">
         <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>12.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>0.57</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B22" t="n">
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>0.78</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="D23" t="n">
-        <v>0.61</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B24" t="n">
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="D24" t="n">
-        <v>0.61</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>9.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="D25" t="n">
-        <v>0.61</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.5</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B27" t="n">
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="D28" t="n">
-        <v>0.46</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>11.3</v>
+        <v>10</v>
       </c>
       <c r="D29" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>0.43</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>9.800000000000001</v>
+        <v>10.1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>9.199999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>43</v>
+        <v>17</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="D33" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
       <c r="D34" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
       </c>
       <c r="C35" t="n">
-        <v>8.6</v>
+        <v>11.1</v>
       </c>
       <c r="D35" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>10.1</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>8.699999999999999</v>
+        <v>10.9</v>
       </c>
       <c r="D37" t="n">
-        <v>0.35</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>11.1</v>
+        <v>9.1</v>
       </c>
       <c r="D38" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>10.2</v>
+        <v>11.1</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>9.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="D40" t="n">
-        <v>0.21</v>
+        <v>0.19</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>10.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
       </c>
       <c r="C42" t="n">
-        <v>11.1</v>
+        <v>8.4</v>
       </c>
       <c r="D42" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>9.1</v>
+        <v>9.9</v>
       </c>
       <c r="D43" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>8.699999999999999</v>
+        <v>10.1</v>
       </c>
       <c r="D44" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>10.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>0.09</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>10.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33545,13 +33576,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33559,13 +33590,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33573,13 +33604,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>8.4</v>
+        <v>10.6</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33587,13 +33618,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>9.199999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>

--- a/docs/eurojackpot.xlsx
+++ b/docs/eurojackpot.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1003"/>
+  <dimension ref="A1:I1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31533,6 +31533,37 @@
       </c>
       <c r="I1003" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="1004">
+      <c r="A1004" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>Friday</t>
+        </is>
+      </c>
+      <c r="C1004" t="n">
+        <v>21</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>26</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>37</v>
+      </c>
+      <c r="F1004" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>42</v>
+      </c>
+      <c r="H1004" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1004" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -31574,7 +31605,7 @@
         <v>117</v>
       </c>
       <c r="C2" t="n">
-        <v>11.68</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="3">
@@ -31585,7 +31616,7 @@
         <v>115</v>
       </c>
       <c r="C3" t="n">
-        <v>11.48</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="4">
@@ -31596,7 +31627,7 @@
         <v>115</v>
       </c>
       <c r="C4" t="n">
-        <v>11.48</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="5">
@@ -31607,7 +31638,7 @@
         <v>115</v>
       </c>
       <c r="C5" t="n">
-        <v>11.48</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="6">
@@ -31615,10 +31646,10 @@
         <v>21</v>
       </c>
       <c r="B6" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C6" t="n">
-        <v>11.18</v>
+        <v>11.27</v>
       </c>
     </row>
     <row r="7">
@@ -31629,7 +31660,7 @@
         <v>112</v>
       </c>
       <c r="C7" t="n">
-        <v>11.18</v>
+        <v>11.17</v>
       </c>
     </row>
     <row r="8">
@@ -31640,7 +31671,7 @@
         <v>110</v>
       </c>
       <c r="C8" t="n">
-        <v>10.98</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="9">
@@ -31651,7 +31682,7 @@
         <v>109</v>
       </c>
       <c r="C9" t="n">
-        <v>10.88</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="10">
@@ -31662,7 +31693,7 @@
         <v>108</v>
       </c>
       <c r="C10" t="n">
-        <v>10.78</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="11">
@@ -31673,7 +31704,7 @@
         <v>108</v>
       </c>
       <c r="C11" t="n">
-        <v>10.78</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="12">
@@ -31684,7 +31715,7 @@
         <v>108</v>
       </c>
       <c r="C12" t="n">
-        <v>10.78</v>
+        <v>10.77</v>
       </c>
     </row>
     <row r="13">
@@ -31695,7 +31726,7 @@
         <v>107</v>
       </c>
       <c r="C13" t="n">
-        <v>10.68</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="14">
@@ -31706,18 +31737,18 @@
         <v>105</v>
       </c>
       <c r="C14" t="n">
-        <v>10.48</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="B15" t="n">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C15" t="n">
-        <v>10.38</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="16">
@@ -31728,7 +31759,7 @@
         <v>104</v>
       </c>
       <c r="C16" t="n">
-        <v>10.38</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="17">
@@ -31739,18 +31770,18 @@
         <v>104</v>
       </c>
       <c r="C17" t="n">
-        <v>10.38</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="B18" t="n">
         <v>104</v>
       </c>
       <c r="C18" t="n">
-        <v>10.38</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="19">
@@ -31761,7 +31792,7 @@
         <v>103</v>
       </c>
       <c r="C19" t="n">
-        <v>10.28</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="20">
@@ -31772,29 +31803,29 @@
         <v>103</v>
       </c>
       <c r="C20" t="n">
-        <v>10.28</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="B21" t="n">
         <v>103</v>
       </c>
       <c r="C21" t="n">
-        <v>10.28</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="B22" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C22" t="n">
-        <v>10.18</v>
+        <v>10.27</v>
       </c>
     </row>
     <row r="23">
@@ -31805,7 +31836,7 @@
         <v>101</v>
       </c>
       <c r="C23" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="24">
@@ -31816,7 +31847,7 @@
         <v>101</v>
       </c>
       <c r="C24" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="25">
@@ -31827,7 +31858,7 @@
         <v>101</v>
       </c>
       <c r="C25" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="26">
@@ -31838,7 +31869,7 @@
         <v>101</v>
       </c>
       <c r="C26" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="27">
@@ -31849,7 +31880,7 @@
         <v>101</v>
       </c>
       <c r="C27" t="n">
-        <v>10.08</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="28">
@@ -31860,7 +31891,7 @@
         <v>100</v>
       </c>
       <c r="C28" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -31871,7 +31902,7 @@
         <v>100</v>
       </c>
       <c r="C29" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -31882,7 +31913,7 @@
         <v>99</v>
       </c>
       <c r="C30" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="31">
@@ -31893,7 +31924,7 @@
         <v>99</v>
       </c>
       <c r="C31" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="32">
@@ -31904,7 +31935,7 @@
         <v>98</v>
       </c>
       <c r="C32" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="33">
@@ -31915,7 +31946,7 @@
         <v>98</v>
       </c>
       <c r="C33" t="n">
-        <v>9.779999999999999</v>
+        <v>9.77</v>
       </c>
     </row>
     <row r="34">
@@ -31926,7 +31957,7 @@
         <v>96</v>
       </c>
       <c r="C34" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="35">
@@ -31937,7 +31968,7 @@
         <v>96</v>
       </c>
       <c r="C35" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
     </row>
     <row r="36">
@@ -31948,18 +31979,18 @@
         <v>95</v>
       </c>
       <c r="C36" t="n">
-        <v>9.48</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B37" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C37" t="n">
-        <v>9.380000000000001</v>
+        <v>9.470000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -31970,7 +32001,7 @@
         <v>94</v>
       </c>
       <c r="C38" t="n">
-        <v>9.380000000000001</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="39">
@@ -31981,18 +32012,18 @@
         <v>94</v>
       </c>
       <c r="C39" t="n">
-        <v>9.380000000000001</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B40" t="n">
         <v>94</v>
       </c>
       <c r="C40" t="n">
-        <v>9.380000000000001</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="41">
@@ -32003,7 +32034,7 @@
         <v>93</v>
       </c>
       <c r="C41" t="n">
-        <v>9.279999999999999</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="42">
@@ -32014,7 +32045,7 @@
         <v>93</v>
       </c>
       <c r="C42" t="n">
-        <v>9.279999999999999</v>
+        <v>9.27</v>
       </c>
     </row>
     <row r="43">
@@ -32025,7 +32056,7 @@
         <v>91</v>
       </c>
       <c r="C43" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="44">
@@ -32036,7 +32067,7 @@
         <v>91</v>
       </c>
       <c r="C44" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="45">
@@ -32044,10 +32075,10 @@
         <v>26</v>
       </c>
       <c r="B45" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C45" t="n">
-        <v>8.98</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="46">
@@ -32058,7 +32089,7 @@
         <v>89</v>
       </c>
       <c r="C46" t="n">
-        <v>8.880000000000001</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -32069,7 +32100,7 @@
         <v>89</v>
       </c>
       <c r="C47" t="n">
-        <v>8.880000000000001</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -32080,7 +32111,7 @@
         <v>89</v>
       </c>
       <c r="C48" t="n">
-        <v>8.880000000000001</v>
+        <v>8.869999999999999</v>
       </c>
     </row>
     <row r="49">
@@ -32091,7 +32122,7 @@
         <v>88</v>
       </c>
       <c r="C49" t="n">
-        <v>8.779999999999999</v>
+        <v>8.77</v>
       </c>
     </row>
     <row r="50">
@@ -32102,7 +32133,7 @@
         <v>87</v>
       </c>
       <c r="C50" t="n">
-        <v>8.68</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="51">
@@ -32152,10 +32183,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C2" t="n">
-        <v>21.66</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="3">
@@ -32166,7 +32197,7 @@
         <v>203</v>
       </c>
       <c r="C3" t="n">
-        <v>20.26</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="4">
@@ -32177,7 +32208,7 @@
         <v>198</v>
       </c>
       <c r="C4" t="n">
-        <v>19.76</v>
+        <v>19.74</v>
       </c>
     </row>
     <row r="5">
@@ -32185,10 +32216,10 @@
         <v>7</v>
       </c>
       <c r="B5" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C5" t="n">
-        <v>19.36</v>
+        <v>19.44</v>
       </c>
     </row>
     <row r="6">
@@ -32199,7 +32230,7 @@
         <v>190</v>
       </c>
       <c r="C6" t="n">
-        <v>18.96</v>
+        <v>18.94</v>
       </c>
     </row>
     <row r="7">
@@ -32210,7 +32241,7 @@
         <v>184</v>
       </c>
       <c r="C7" t="n">
-        <v>18.36</v>
+        <v>18.34</v>
       </c>
     </row>
     <row r="8">
@@ -32221,7 +32252,7 @@
         <v>184</v>
       </c>
       <c r="C8" t="n">
-        <v>18.36</v>
+        <v>18.34</v>
       </c>
     </row>
     <row r="9">
@@ -32232,7 +32263,7 @@
         <v>167</v>
       </c>
       <c r="C9" t="n">
-        <v>16.67</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="10">
@@ -32243,7 +32274,7 @@
         <v>165</v>
       </c>
       <c r="C10" t="n">
-        <v>16.47</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="11">
@@ -32254,7 +32285,7 @@
         <v>149</v>
       </c>
       <c r="C11" t="n">
-        <v>14.87</v>
+        <v>14.86</v>
       </c>
     </row>
     <row r="12">
@@ -32265,7 +32296,7 @@
         <v>87</v>
       </c>
       <c r="C12" t="n">
-        <v>8.68</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="13">
@@ -32276,7 +32307,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="n">
-        <v>6.59</v>
+        <v>6.58</v>
       </c>
     </row>
   </sheetData>
@@ -32315,10 +32346,10 @@
         <v>5</v>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C2" t="n">
-        <v>20.83</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3">
@@ -32329,7 +32360,7 @@
         <v>92</v>
       </c>
       <c r="C3" t="n">
-        <v>19.17</v>
+        <v>19.13</v>
       </c>
     </row>
     <row r="4">
@@ -32340,7 +32371,7 @@
         <v>87</v>
       </c>
       <c r="C4" t="n">
-        <v>18.12</v>
+        <v>18.09</v>
       </c>
     </row>
     <row r="5">
@@ -32351,7 +32382,7 @@
         <v>83</v>
       </c>
       <c r="C5" t="n">
-        <v>17.29</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="6">
@@ -32359,10 +32390,10 @@
         <v>7</v>
       </c>
       <c r="B6" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C6" t="n">
-        <v>17.08</v>
+        <v>17.26</v>
       </c>
     </row>
     <row r="7">
@@ -32373,7 +32404,7 @@
         <v>79</v>
       </c>
       <c r="C7" t="n">
-        <v>16.46</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="8">
@@ -32384,7 +32415,7 @@
         <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>16.25</v>
+        <v>16.22</v>
       </c>
     </row>
     <row r="9">
@@ -32395,7 +32426,7 @@
         <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>15.83</v>
+        <v>15.8</v>
       </c>
     </row>
     <row r="10">
@@ -32406,7 +32437,7 @@
         <v>75</v>
       </c>
       <c r="C10" t="n">
-        <v>15.62</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="11">
@@ -32417,7 +32448,7 @@
         <v>72</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="12">
@@ -32428,7 +32459,7 @@
         <v>70</v>
       </c>
       <c r="C12" t="n">
-        <v>14.58</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="13">
@@ -32439,7 +32470,7 @@
         <v>66</v>
       </c>
       <c r="C13" t="n">
-        <v>13.75</v>
+        <v>13.72</v>
       </c>
     </row>
   </sheetData>
@@ -32711,7 +32742,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>39 &amp; 47</t>
+          <t>21 &amp; 39</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -32935,13 +32966,13 @@
         <v>44</v>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C2" t="n">
         <v>10.4</v>
       </c>
       <c r="D2" t="n">
-        <v>3.26</v>
+        <v>3.36</v>
       </c>
     </row>
     <row r="3">
@@ -32949,13 +32980,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" t="n">
         <v>9.5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.86</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="4">
@@ -32963,13 +32994,13 @@
         <v>13</v>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
         <v>9.5</v>
       </c>
       <c r="D4" t="n">
-        <v>2.41</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="5">
@@ -32977,13 +33008,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
         <v>10.3</v>
       </c>
       <c r="D5" t="n">
-        <v>2.24</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="6">
@@ -32991,410 +33022,410 @@
         <v>1</v>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
         <v>9.1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.53</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>10.3</v>
       </c>
       <c r="D7" t="n">
-        <v>1.91</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>10.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>9.5</v>
+        <v>10.4</v>
       </c>
       <c r="D9" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>49</v>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>9.699999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="D10" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
-        <v>10.4</v>
+        <v>9.5</v>
       </c>
       <c r="D11" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="B12" t="n">
         <v>13</v>
       </c>
       <c r="C12" t="n">
-        <v>9.800000000000001</v>
+        <v>11.2</v>
       </c>
       <c r="D12" t="n">
-        <v>1.33</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>9.1</v>
+        <v>10.3</v>
       </c>
       <c r="D13" t="n">
-        <v>1.43</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>9.5</v>
+        <v>10.7</v>
       </c>
       <c r="D14" t="n">
-        <v>1.37</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>11.2</v>
+        <v>11.5</v>
       </c>
       <c r="D15" t="n">
-        <v>1.07</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="B16" t="n">
         <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>10.3</v>
+        <v>12.3</v>
       </c>
       <c r="D16" t="n">
-        <v>0.88</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>10.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="B18" t="n">
         <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>48</v>
+        <v>7</v>
       </c>
       <c r="B19" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>12.3</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>0.65</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>8.9</v>
+        <v>11</v>
       </c>
       <c r="D20" t="n">
-        <v>0.89</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="B21" t="n">
         <v>7</v>
       </c>
       <c r="C21" t="n">
-        <v>9.800000000000001</v>
+        <v>11.3</v>
       </c>
       <c r="D21" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="B22" t="n">
         <v>7</v>
       </c>
       <c r="C22" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="D22" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B23" t="n">
         <v>6</v>
       </c>
       <c r="C23" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>0.55</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>19</v>
+        <v>46</v>
       </c>
       <c r="B24" t="n">
         <v>6</v>
       </c>
       <c r="C24" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B25" t="n">
         <v>6</v>
       </c>
       <c r="C25" t="n">
-        <v>11.3</v>
+        <v>9.4</v>
       </c>
       <c r="D25" t="n">
-        <v>0.53</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B26" t="n">
         <v>6</v>
       </c>
       <c r="C26" t="n">
-        <v>9.699999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" t="n">
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="D27" t="n">
-        <v>0.54</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B28" t="n">
         <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>0.53</v>
+        <v>0.58</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>43</v>
+        <v>22</v>
       </c>
       <c r="B29" t="n">
         <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5</v>
+        <v>0.49</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>0.51</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
       </c>
       <c r="C31" t="n">
-        <v>10.1</v>
+        <v>11.1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
       </c>
       <c r="C32" t="n">
-        <v>8.699999999999999</v>
+        <v>10.2</v>
       </c>
       <c r="D32" t="n">
-        <v>0.46</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
       </c>
       <c r="C33" t="n">
-        <v>8.6</v>
+        <v>10.9</v>
       </c>
       <c r="D33" t="n">
-        <v>0.46</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B34" t="n">
         <v>3</v>
       </c>
       <c r="C34" t="n">
-        <v>10.2</v>
+        <v>9.1</v>
       </c>
       <c r="D34" t="n">
-        <v>0.29</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B35" t="n">
         <v>3</v>
@@ -33408,41 +33439,41 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="B36" t="n">
         <v>3</v>
       </c>
       <c r="C36" t="n">
-        <v>9.699999999999999</v>
+        <v>10.6</v>
       </c>
       <c r="D36" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="B37" t="n">
         <v>3</v>
       </c>
       <c r="C37" t="n">
-        <v>10.9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>0.27</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B38" t="n">
         <v>2</v>
       </c>
       <c r="C38" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D38" t="n">
         <v>0.22</v>
@@ -33450,83 +33481,83 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B39" t="n">
         <v>2</v>
       </c>
       <c r="C39" t="n">
-        <v>11.1</v>
+        <v>9.9</v>
       </c>
       <c r="D39" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B40" t="n">
         <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>10.6</v>
+        <v>10.1</v>
       </c>
       <c r="D40" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="B41" t="n">
         <v>2</v>
       </c>
       <c r="C41" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="D41" t="n">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C42" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
       </c>
       <c r="C43" t="n">
-        <v>9.9</v>
+        <v>9</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
       </c>
       <c r="C44" t="n">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="D44" t="n">
         <v>0.1</v>
@@ -33534,41 +33565,41 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
       </c>
       <c r="C45" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="D45" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>9.199999999999999</v>
+        <v>10.4</v>
       </c>
       <c r="D46" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B47" t="n">
         <v>0</v>
       </c>
       <c r="C47" t="n">
-        <v>9</v>
+        <v>11.1</v>
       </c>
       <c r="D47" t="n">
         <v>0</v>
@@ -33576,13 +33607,13 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="B48" t="n">
         <v>0</v>
       </c>
       <c r="C48" t="n">
-        <v>10.4</v>
+        <v>8.9</v>
       </c>
       <c r="D48" t="n">
         <v>0</v>
@@ -33590,13 +33621,13 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B49" t="n">
         <v>0</v>
       </c>
       <c r="C49" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="D49" t="n">
         <v>0</v>
@@ -33604,13 +33635,13 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="B50" t="n">
         <v>0</v>
       </c>
       <c r="C50" t="n">
-        <v>10.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D50" t="n">
         <v>0</v>
@@ -33618,13 +33649,13 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B51" t="n">
         <v>0</v>
       </c>
       <c r="C51" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
